--- a/Final_Test_Reports/Load_Testing_Report_v2.xlsx
+++ b/Final_Test_Reports/Load_Testing_Report_v2.xlsx
@@ -459,10 +459,10 @@
         <v>60</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-06-23T05:13:23.051Z</v>
+        <v>2026-06-23T05:24:45.423Z</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-06-23T05:14:23.052Z</v>
+        <v>2026-06-23T05:25:45.424Z</v>
       </c>
     </row>
   </sheetData>
@@ -511,7 +511,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D2">
-        <v>0.99</v>
+        <v>0.78</v>
       </c>
       <c r="E2" t="str">
         <v>PASSED</v>
@@ -528,7 +528,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D3">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="E3" t="str">
         <v>PASSED</v>
@@ -545,7 +545,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D4">
-        <v>2.5</v>
+        <v>0.57</v>
       </c>
       <c r="E4" t="str">
         <v>PASSED</v>
@@ -562,7 +562,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D5">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="E5" t="str">
         <v>PASSED</v>
@@ -579,7 +579,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D6">
-        <v>0.3</v>
+        <v>0.72</v>
       </c>
       <c r="E6" t="str">
         <v>PASSED</v>
@@ -596,7 +596,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D7">
-        <v>0.75</v>
+        <v>1.79</v>
       </c>
       <c r="E7" t="str">
         <v>PASSED</v>
@@ -613,7 +613,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D8">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="E8" t="str">
         <v>PASSED</v>
@@ -630,7 +630,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D9">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="E9" t="str">
         <v>PASSED</v>
@@ -647,7 +647,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D10">
-        <v>0.77</v>
+        <v>0.15</v>
       </c>
       <c r="E10" t="str">
         <v>PASSED</v>
@@ -664,7 +664,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D11">
-        <v>0.52</v>
+        <v>1.18</v>
       </c>
       <c r="E11" t="str">
         <v>PASSED</v>
@@ -681,7 +681,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D12">
-        <v>1.37</v>
+        <v>2.12</v>
       </c>
       <c r="E12" t="str">
         <v>PASSED</v>
@@ -698,7 +698,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D13">
-        <v>1.09</v>
+        <v>1.84</v>
       </c>
       <c r="E13" t="str">
         <v>PASSED</v>
@@ -715,7 +715,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D14">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="E14" t="str">
         <v>PASSED</v>
@@ -732,7 +732,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="E15" t="str">
         <v>PASSED</v>
@@ -749,7 +749,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D16">
-        <v>0.36</v>
+        <v>2.05</v>
       </c>
       <c r="E16" t="str">
         <v>PASSED</v>
@@ -766,7 +766,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D17">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="E17" t="str">
         <v>PASSED</v>
@@ -783,7 +783,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D18">
-        <v>1.4</v>
+        <v>0.37</v>
       </c>
       <c r="E18" t="str">
         <v>PASSED</v>
@@ -800,7 +800,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D19">
-        <v>1.7</v>
+        <v>0.81</v>
       </c>
       <c r="E19" t="str">
         <v>PASSED</v>
@@ -817,7 +817,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D20">
-        <v>1.73</v>
+        <v>0.53</v>
       </c>
       <c r="E20" t="str">
         <v>PASSED</v>
@@ -834,7 +834,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D21">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="E21" t="str">
         <v>PASSED</v>
@@ -851,7 +851,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D22">
-        <v>2.02</v>
+        <v>0.43</v>
       </c>
       <c r="E22" t="str">
         <v>PASSED</v>
@@ -868,7 +868,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D23">
-        <v>2.44</v>
+        <v>1.94</v>
       </c>
       <c r="E23" t="str">
         <v>PASSED</v>
@@ -885,7 +885,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D24">
-        <v>0.43</v>
+        <v>2.11</v>
       </c>
       <c r="E24" t="str">
         <v>PASSED</v>
@@ -902,7 +902,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D25">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="E25" t="str">
         <v>PASSED</v>
@@ -919,7 +919,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D26">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="E26" t="str">
         <v>PASSED</v>
@@ -936,7 +936,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D27">
-        <v>1.26</v>
+        <v>2.18</v>
       </c>
       <c r="E27" t="str">
         <v>PASSED</v>
@@ -953,7 +953,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D28">
-        <v>0.72</v>
+        <v>1.23</v>
       </c>
       <c r="E28" t="str">
         <v>PASSED</v>
@@ -970,7 +970,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D29">
-        <v>0.64</v>
+        <v>0.16</v>
       </c>
       <c r="E29" t="str">
         <v>PASSED</v>
@@ -987,7 +987,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D30">
-        <v>0.86</v>
+        <v>2.08</v>
       </c>
       <c r="E30" t="str">
         <v>PASSED</v>
@@ -1004,7 +1004,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D31">
-        <v>1.52</v>
+        <v>0.33</v>
       </c>
       <c r="E31" t="str">
         <v>PASSED</v>
@@ -1021,7 +1021,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D32">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="E32" t="str">
         <v>PASSED</v>
@@ -1038,7 +1038,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D33">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="E33" t="str">
         <v>PASSED</v>
@@ -1055,7 +1055,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D34">
-        <v>0.45</v>
+        <v>0.94</v>
       </c>
       <c r="E34" t="str">
         <v>PASSED</v>
@@ -1072,7 +1072,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D35">
-        <v>2.19</v>
+        <v>1.41</v>
       </c>
       <c r="E35" t="str">
         <v>PASSED</v>
@@ -1089,7 +1089,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D36">
-        <v>0.95</v>
+        <v>1.52</v>
       </c>
       <c r="E36" t="str">
         <v>PASSED</v>
@@ -1106,7 +1106,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D37">
-        <v>0.42</v>
+        <v>1.89</v>
       </c>
       <c r="E37" t="str">
         <v>PASSED</v>
@@ -1123,7 +1123,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D38">
-        <v>0.74</v>
+        <v>1.6</v>
       </c>
       <c r="E38" t="str">
         <v>PASSED</v>
@@ -1140,7 +1140,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D39">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="E39" t="str">
         <v>PASSED</v>
@@ -1157,7 +1157,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D40">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="E40" t="str">
         <v>PASSED</v>
@@ -1174,7 +1174,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D41">
-        <v>1.7</v>
+        <v>2.27</v>
       </c>
       <c r="E41" t="str">
         <v>PASSED</v>
@@ -1191,7 +1191,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D42">
-        <v>0.3</v>
+        <v>0.88</v>
       </c>
       <c r="E42" t="str">
         <v>PASSED</v>
@@ -1208,7 +1208,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D43">
-        <v>2.25</v>
+        <v>0.45</v>
       </c>
       <c r="E43" t="str">
         <v>PASSED</v>
@@ -1225,7 +1225,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D44">
-        <v>0.85</v>
+        <v>0.66</v>
       </c>
       <c r="E44" t="str">
         <v>PASSED</v>
@@ -1242,7 +1242,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D45">
-        <v>2.13</v>
+        <v>0.68</v>
       </c>
       <c r="E45" t="str">
         <v>PASSED</v>
@@ -1259,7 +1259,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D46">
-        <v>2.3</v>
+        <v>0.78</v>
       </c>
       <c r="E46" t="str">
         <v>PASSED</v>
@@ -1276,7 +1276,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="E47" t="str">
         <v>PASSED</v>
@@ -1293,7 +1293,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D48">
-        <v>1.09</v>
+        <v>1.98</v>
       </c>
       <c r="E48" t="str">
         <v>PASSED</v>
@@ -1310,7 +1310,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D49">
-        <v>1.94</v>
+        <v>2.29</v>
       </c>
       <c r="E49" t="str">
         <v>PASSED</v>
@@ -1327,7 +1327,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D50">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="E50" t="str">
         <v>PASSED</v>
@@ -1344,7 +1344,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D51">
-        <v>2.26</v>
+        <v>1.36</v>
       </c>
       <c r="E51" t="str">
         <v>PASSED</v>
@@ -1361,7 +1361,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D52">
-        <v>1.05</v>
+        <v>0.26</v>
       </c>
       <c r="E52" t="str">
         <v>PASSED</v>
@@ -1378,7 +1378,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D53">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="E53" t="str">
         <v>PASSED</v>
@@ -1395,7 +1395,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D54">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="E54" t="str">
         <v>PASSED</v>
@@ -1412,7 +1412,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D55">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="E55" t="str">
         <v>PASSED</v>
@@ -1429,7 +1429,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D56">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="E56" t="str">
         <v>PASSED</v>
@@ -1446,7 +1446,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D57">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="E57" t="str">
         <v>PASSED</v>
@@ -1463,7 +1463,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D58">
-        <v>0.6</v>
+        <v>1.72</v>
       </c>
       <c r="E58" t="str">
         <v>PASSED</v>
@@ -1480,7 +1480,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D59">
-        <v>2.44</v>
+        <v>1.58</v>
       </c>
       <c r="E59" t="str">
         <v>PASSED</v>
@@ -1497,7 +1497,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D60">
-        <v>1.02</v>
+        <v>0.82</v>
       </c>
       <c r="E60" t="str">
         <v>PASSED</v>
@@ -1514,7 +1514,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D61">
-        <v>1.13</v>
+        <v>1.52</v>
       </c>
       <c r="E61" t="str">
         <v>PASSED</v>
@@ -1531,7 +1531,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D62">
-        <v>0.64</v>
+        <v>0.94</v>
       </c>
       <c r="E62" t="str">
         <v>PASSED</v>
@@ -1548,7 +1548,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D63">
-        <v>0.63</v>
+        <v>0.26</v>
       </c>
       <c r="E63" t="str">
         <v>PASSED</v>
@@ -1565,7 +1565,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D64">
-        <v>0.97</v>
+        <v>1.17</v>
       </c>
       <c r="E64" t="str">
         <v>PASSED</v>
@@ -1582,7 +1582,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D65">
-        <v>1.03</v>
+        <v>2.19</v>
       </c>
       <c r="E65" t="str">
         <v>PASSED</v>
@@ -1599,7 +1599,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D66">
-        <v>0.36</v>
+        <v>1.5</v>
       </c>
       <c r="E66" t="str">
         <v>PASSED</v>
@@ -1616,7 +1616,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D67">
-        <v>2.19</v>
+        <v>1.51</v>
       </c>
       <c r="E67" t="str">
         <v>PASSED</v>
@@ -1633,7 +1633,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D68">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="E68" t="str">
         <v>PASSED</v>
@@ -1650,7 +1650,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D69">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="E69" t="str">
         <v>PASSED</v>
@@ -1667,7 +1667,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D70">
-        <v>0.27</v>
+        <v>1.34</v>
       </c>
       <c r="E70" t="str">
         <v>PASSED</v>
@@ -1684,7 +1684,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D71">
-        <v>0.99</v>
+        <v>1.45</v>
       </c>
       <c r="E71" t="str">
         <v>PASSED</v>
@@ -1701,7 +1701,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D72">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="E72" t="str">
         <v>PASSED</v>
@@ -1718,7 +1718,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D73">
-        <v>2.26</v>
+        <v>2.47</v>
       </c>
       <c r="E73" t="str">
         <v>PASSED</v>
@@ -1735,7 +1735,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D74">
-        <v>1.87</v>
+        <v>0.23</v>
       </c>
       <c r="E74" t="str">
         <v>PASSED</v>
@@ -1752,7 +1752,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D75">
-        <v>0.5</v>
+        <v>1.58</v>
       </c>
       <c r="E75" t="str">
         <v>PASSED</v>
@@ -1769,7 +1769,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D76">
-        <v>2.01</v>
+        <v>1.53</v>
       </c>
       <c r="E76" t="str">
         <v>PASSED</v>
@@ -1786,7 +1786,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D77">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="E77" t="str">
         <v>PASSED</v>
@@ -1803,7 +1803,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D78">
-        <v>0.76</v>
+        <v>2.21</v>
       </c>
       <c r="E78" t="str">
         <v>PASSED</v>
@@ -1820,7 +1820,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D79">
-        <v>2.41</v>
+        <v>1.05</v>
       </c>
       <c r="E79" t="str">
         <v>PASSED</v>
@@ -1837,7 +1837,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D80">
-        <v>0.92</v>
+        <v>2.33</v>
       </c>
       <c r="E80" t="str">
         <v>PASSED</v>
@@ -1854,7 +1854,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D81">
-        <v>0.88</v>
+        <v>0.21</v>
       </c>
       <c r="E81" t="str">
         <v>PASSED</v>
@@ -1871,7 +1871,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D82">
-        <v>2.39</v>
+        <v>0.5</v>
       </c>
       <c r="E82" t="str">
         <v>PASSED</v>
@@ -1888,7 +1888,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D83">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="E83" t="str">
         <v>PASSED</v>
@@ -1905,7 +1905,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D84">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="E84" t="str">
         <v>PASSED</v>
@@ -1922,7 +1922,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D85">
-        <v>0.98</v>
+        <v>2.44</v>
       </c>
       <c r="E85" t="str">
         <v>PASSED</v>
@@ -1939,7 +1939,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D86">
-        <v>1.29</v>
+        <v>1.88</v>
       </c>
       <c r="E86" t="str">
         <v>PASSED</v>
@@ -1956,7 +1956,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D87">
-        <v>1.92</v>
+        <v>0.59</v>
       </c>
       <c r="E87" t="str">
         <v>PASSED</v>
@@ -1973,7 +1973,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D88">
-        <v>2.35</v>
+        <v>1.69</v>
       </c>
       <c r="E88" t="str">
         <v>PASSED</v>
@@ -1990,7 +1990,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D89">
-        <v>0.74</v>
+        <v>1.66</v>
       </c>
       <c r="E89" t="str">
         <v>PASSED</v>
@@ -2007,7 +2007,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D90">
-        <v>1.89</v>
+        <v>0.83</v>
       </c>
       <c r="E90" t="str">
         <v>PASSED</v>
@@ -2024,7 +2024,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D91">
-        <v>1.33</v>
+        <v>2.44</v>
       </c>
       <c r="E91" t="str">
         <v>PASSED</v>
@@ -2041,7 +2041,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D92">
-        <v>0.29</v>
+        <v>1.13</v>
       </c>
       <c r="E92" t="str">
         <v>PASSED</v>
@@ -2058,7 +2058,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D93">
-        <v>0.81</v>
+        <v>1.69</v>
       </c>
       <c r="E93" t="str">
         <v>PASSED</v>
@@ -2075,7 +2075,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D94">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="E94" t="str">
         <v>PASSED</v>
@@ -2092,7 +2092,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D95">
-        <v>1.43</v>
+        <v>0.36</v>
       </c>
       <c r="E95" t="str">
         <v>PASSED</v>
@@ -2109,7 +2109,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D96">
-        <v>1.58</v>
+        <v>0.4</v>
       </c>
       <c r="E96" t="str">
         <v>PASSED</v>
@@ -2126,7 +2126,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D97">
-        <v>2.29</v>
+        <v>0.51</v>
       </c>
       <c r="E97" t="str">
         <v>PASSED</v>
@@ -2143,7 +2143,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D98">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="E98" t="str">
         <v>PASSED</v>
@@ -2160,7 +2160,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D99">
-        <v>1.81</v>
+        <v>0.74</v>
       </c>
       <c r="E99" t="str">
         <v>PASSED</v>
@@ -2177,7 +2177,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D100">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="E100" t="str">
         <v>PASSED</v>
@@ -2194,7 +2194,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D101">
-        <v>0.86</v>
+        <v>2.03</v>
       </c>
       <c r="E101" t="str">
         <v>PASSED</v>
@@ -2211,7 +2211,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D102">
-        <v>1.95</v>
+        <v>0.39</v>
       </c>
       <c r="E102" t="str">
         <v>PASSED</v>
@@ -2228,7 +2228,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D103">
-        <v>0.81</v>
+        <v>2.47</v>
       </c>
       <c r="E103" t="str">
         <v>PASSED</v>
@@ -2262,7 +2262,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D105">
-        <v>0.28</v>
+        <v>1.4</v>
       </c>
       <c r="E105" t="str">
         <v>PASSED</v>
@@ -2279,7 +2279,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D106">
-        <v>1.94</v>
+        <v>0.61</v>
       </c>
       <c r="E106" t="str">
         <v>PASSED</v>
@@ -2296,7 +2296,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D107">
-        <v>1.54</v>
+        <v>0.18</v>
       </c>
       <c r="E107" t="str">
         <v>PASSED</v>
@@ -2313,7 +2313,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D108">
-        <v>0.91</v>
+        <v>1.39</v>
       </c>
       <c r="E108" t="str">
         <v>PASSED</v>
@@ -2330,7 +2330,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D109">
-        <v>1.98</v>
+        <v>0.43</v>
       </c>
       <c r="E109" t="str">
         <v>PASSED</v>
@@ -2347,7 +2347,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D110">
-        <v>1.17</v>
+        <v>1.8</v>
       </c>
       <c r="E110" t="str">
         <v>PASSED</v>
@@ -2364,7 +2364,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D111">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="E111" t="str">
         <v>PASSED</v>
@@ -2381,7 +2381,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D112">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="E112" t="str">
         <v>PASSED</v>
@@ -2398,7 +2398,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D113">
-        <v>2.29</v>
+        <v>1.17</v>
       </c>
       <c r="E113" t="str">
         <v>PASSED</v>
@@ -2415,7 +2415,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D114">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="E114" t="str">
         <v>PASSED</v>
@@ -2432,7 +2432,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D115">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="E115" t="str">
         <v>PASSED</v>
@@ -2449,7 +2449,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D116">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="E116" t="str">
         <v>PASSED</v>
@@ -2466,7 +2466,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D117">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="E117" t="str">
         <v>PASSED</v>
@@ -2483,7 +2483,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D118">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="E118" t="str">
         <v>PASSED</v>
@@ -2500,7 +2500,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D119">
-        <v>1.27</v>
+        <v>0.68</v>
       </c>
       <c r="E119" t="str">
         <v>PASSED</v>
@@ -2517,7 +2517,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D120">
-        <v>1.1</v>
+        <v>2.37</v>
       </c>
       <c r="E120" t="str">
         <v>PASSED</v>
@@ -2534,7 +2534,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D121">
-        <v>0.38</v>
+        <v>2.49</v>
       </c>
       <c r="E121" t="str">
         <v>PASSED</v>
@@ -2551,7 +2551,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D122">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="E122" t="str">
         <v>PASSED</v>
@@ -2568,7 +2568,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D123">
-        <v>1.38</v>
+        <v>0.46</v>
       </c>
       <c r="E123" t="str">
         <v>PASSED</v>
@@ -2585,7 +2585,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D124">
-        <v>1.63</v>
+        <v>0.41</v>
       </c>
       <c r="E124" t="str">
         <v>PASSED</v>
@@ -2602,7 +2602,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D125">
-        <v>1.03</v>
+        <v>1.97</v>
       </c>
       <c r="E125" t="str">
         <v>PASSED</v>
@@ -2619,7 +2619,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>2.09</v>
       </c>
       <c r="E126" t="str">
         <v>PASSED</v>
@@ -2636,7 +2636,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D127">
-        <v>0.37</v>
+        <v>1.82</v>
       </c>
       <c r="E127" t="str">
         <v>PASSED</v>
@@ -2653,7 +2653,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D128">
-        <v>1.96</v>
+        <v>1.13</v>
       </c>
       <c r="E128" t="str">
         <v>PASSED</v>
@@ -2670,7 +2670,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D129">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="E129" t="str">
         <v>PASSED</v>
@@ -2687,7 +2687,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D130">
-        <v>0.86</v>
+        <v>1.79</v>
       </c>
       <c r="E130" t="str">
         <v>PASSED</v>
@@ -2704,7 +2704,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D131">
-        <v>0.34</v>
+        <v>0.55</v>
       </c>
       <c r="E131" t="str">
         <v>PASSED</v>
@@ -2721,7 +2721,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D132">
-        <v>0.17</v>
+        <v>0.91</v>
       </c>
       <c r="E132" t="str">
         <v>PASSED</v>
@@ -2738,7 +2738,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D133">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="E133" t="str">
         <v>PASSED</v>
@@ -2755,7 +2755,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D134">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="E134" t="str">
         <v>PASSED</v>
@@ -2772,7 +2772,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D135">
-        <v>1.15</v>
+        <v>0.41</v>
       </c>
       <c r="E135" t="str">
         <v>PASSED</v>
@@ -2789,7 +2789,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D136">
-        <v>0.26</v>
+        <v>1.03</v>
       </c>
       <c r="E136" t="str">
         <v>PASSED</v>
@@ -2806,7 +2806,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D137">
-        <v>1.8</v>
+        <v>1.08</v>
       </c>
       <c r="E137" t="str">
         <v>PASSED</v>
@@ -2823,7 +2823,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D138">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="E138" t="str">
         <v>PASSED</v>
@@ -2840,7 +2840,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D139">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="E139" t="str">
         <v>PASSED</v>
@@ -2857,7 +2857,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D140">
-        <v>0.42</v>
+        <v>1.81</v>
       </c>
       <c r="E140" t="str">
         <v>PASSED</v>
@@ -2874,7 +2874,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D141">
-        <v>2.03</v>
+        <v>0.83</v>
       </c>
       <c r="E141" t="str">
         <v>PASSED</v>
@@ -2891,7 +2891,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D142">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="E142" t="str">
         <v>PASSED</v>
@@ -2908,7 +2908,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D143">
-        <v>2.22</v>
+        <v>0.65</v>
       </c>
       <c r="E143" t="str">
         <v>PASSED</v>
@@ -2925,7 +2925,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D144">
-        <v>1.54</v>
+        <v>2.11</v>
       </c>
       <c r="E144" t="str">
         <v>PASSED</v>
@@ -2942,7 +2942,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D145">
-        <v>0.11</v>
+        <v>1.96</v>
       </c>
       <c r="E145" t="str">
         <v>PASSED</v>
@@ -2959,7 +2959,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D146">
-        <v>1.99</v>
+        <v>0.1</v>
       </c>
       <c r="E146" t="str">
         <v>PASSED</v>
@@ -2976,7 +2976,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D147">
-        <v>0.46</v>
+        <v>0.85</v>
       </c>
       <c r="E147" t="str">
         <v>PASSED</v>
@@ -2993,7 +2993,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D148">
-        <v>2.43</v>
+        <v>0.17</v>
       </c>
       <c r="E148" t="str">
         <v>PASSED</v>
@@ -3010,7 +3010,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D149">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="E149" t="str">
         <v>PASSED</v>
@@ -3027,7 +3027,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D150">
-        <v>1.13</v>
+        <v>2.43</v>
       </c>
       <c r="E150" t="str">
         <v>PASSED</v>
@@ -3044,7 +3044,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D151">
-        <v>0.65</v>
+        <v>2.34</v>
       </c>
       <c r="E151" t="str">
         <v>PASSED</v>
@@ -3061,7 +3061,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D152">
-        <v>2.05</v>
+        <v>0.67</v>
       </c>
       <c r="E152" t="str">
         <v>PASSED</v>
@@ -3078,7 +3078,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D153">
-        <v>0.23</v>
+        <v>1.66</v>
       </c>
       <c r="E153" t="str">
         <v>PASSED</v>
@@ -3095,7 +3095,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D154">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="E154" t="str">
         <v>PASSED</v>
@@ -3112,7 +3112,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D155">
-        <v>0.83</v>
+        <v>1.74</v>
       </c>
       <c r="E155" t="str">
         <v>PASSED</v>
@@ -3129,7 +3129,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D156">
-        <v>1.92</v>
+        <v>0.4</v>
       </c>
       <c r="E156" t="str">
         <v>PASSED</v>
@@ -3146,7 +3146,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D157">
-        <v>0.28</v>
+        <v>1.64</v>
       </c>
       <c r="E157" t="str">
         <v>PASSED</v>
@@ -3163,7 +3163,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D158">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="E158" t="str">
         <v>PASSED</v>
@@ -3180,7 +3180,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D159">
-        <v>0.34</v>
+        <v>1.88</v>
       </c>
       <c r="E159" t="str">
         <v>PASSED</v>
@@ -3197,7 +3197,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D160">
-        <v>1.76</v>
+        <v>0.69</v>
       </c>
       <c r="E160" t="str">
         <v>PASSED</v>
@@ -3214,7 +3214,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D161">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="E161" t="str">
         <v>PASSED</v>
@@ -3231,7 +3231,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D162">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="E162" t="str">
         <v>PASSED</v>
@@ -3248,7 +3248,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D163">
-        <v>0.94</v>
+        <v>0.81</v>
       </c>
       <c r="E163" t="str">
         <v>PASSED</v>
@@ -3265,7 +3265,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D164">
-        <v>2.42</v>
+        <v>1.46</v>
       </c>
       <c r="E164" t="str">
         <v>PASSED</v>
@@ -3282,7 +3282,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D165">
-        <v>0.97</v>
+        <v>1.7</v>
       </c>
       <c r="E165" t="str">
         <v>PASSED</v>
@@ -3299,7 +3299,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D166">
-        <v>2.13</v>
+        <v>0.56</v>
       </c>
       <c r="E166" t="str">
         <v>PASSED</v>
@@ -3316,7 +3316,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D167">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="E167" t="str">
         <v>PASSED</v>
@@ -3333,7 +3333,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D168">
-        <v>0.31</v>
+        <v>0.84</v>
       </c>
       <c r="E168" t="str">
         <v>PASSED</v>
@@ -3350,7 +3350,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D169">
-        <v>0.81</v>
+        <v>1.9</v>
       </c>
       <c r="E169" t="str">
         <v>PASSED</v>
@@ -3367,7 +3367,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D170">
-        <v>2.01</v>
+        <v>0.32</v>
       </c>
       <c r="E170" t="str">
         <v>PASSED</v>
@@ -3384,7 +3384,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D171">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="E171" t="str">
         <v>PASSED</v>
@@ -3401,7 +3401,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D172">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="E172" t="str">
         <v>PASSED</v>
@@ -3418,7 +3418,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D173">
-        <v>2.24</v>
+        <v>1.38</v>
       </c>
       <c r="E173" t="str">
         <v>PASSED</v>
@@ -3435,7 +3435,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D174">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="E174" t="str">
         <v>PASSED</v>
@@ -3452,7 +3452,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D175">
-        <v>0.12</v>
+        <v>0.92</v>
       </c>
       <c r="E175" t="str">
         <v>PASSED</v>
@@ -3469,7 +3469,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="E176" t="str">
         <v>PASSED</v>
@@ -3486,7 +3486,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D177">
-        <v>1.95</v>
+        <v>0.97</v>
       </c>
       <c r="E177" t="str">
         <v>PASSED</v>
@@ -3503,7 +3503,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D178">
-        <v>2.08</v>
+        <v>1.09</v>
       </c>
       <c r="E178" t="str">
         <v>PASSED</v>
@@ -3520,7 +3520,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D179">
-        <v>0.7</v>
+        <v>1.64</v>
       </c>
       <c r="E179" t="str">
         <v>PASSED</v>
@@ -3537,7 +3537,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D180">
-        <v>1.94</v>
+        <v>2.21</v>
       </c>
       <c r="E180" t="str">
         <v>PASSED</v>
@@ -3554,7 +3554,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D181">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="E181" t="str">
         <v>PASSED</v>
@@ -3571,7 +3571,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D182">
-        <v>0.38</v>
+        <v>0.71</v>
       </c>
       <c r="E182" t="str">
         <v>PASSED</v>
@@ -3588,7 +3588,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D183">
-        <v>0.99</v>
+        <v>1.47</v>
       </c>
       <c r="E183" t="str">
         <v>PASSED</v>
@@ -3605,7 +3605,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D184">
-        <v>0.63</v>
+        <v>2.33</v>
       </c>
       <c r="E184" t="str">
         <v>PASSED</v>
@@ -3622,7 +3622,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D185">
-        <v>1.27</v>
+        <v>0.39</v>
       </c>
       <c r="E185" t="str">
         <v>PASSED</v>
@@ -3639,7 +3639,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D186">
-        <v>1.37</v>
+        <v>2.47</v>
       </c>
       <c r="E186" t="str">
         <v>PASSED</v>
@@ -3656,7 +3656,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D187">
-        <v>2.01</v>
+        <v>1.11</v>
       </c>
       <c r="E187" t="str">
         <v>PASSED</v>
@@ -3673,7 +3673,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D188">
-        <v>1.36</v>
+        <v>2.37</v>
       </c>
       <c r="E188" t="str">
         <v>PASSED</v>
@@ -3690,7 +3690,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D189">
-        <v>1.06</v>
+        <v>1.52</v>
       </c>
       <c r="E189" t="str">
         <v>PASSED</v>
@@ -3707,7 +3707,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D190">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="E190" t="str">
         <v>PASSED</v>
@@ -3724,7 +3724,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D191">
-        <v>0.97</v>
+        <v>1.33</v>
       </c>
       <c r="E191" t="str">
         <v>PASSED</v>
@@ -3741,7 +3741,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D192">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="E192" t="str">
         <v>PASSED</v>
@@ -3758,7 +3758,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D193">
-        <v>1.09</v>
+        <v>2.16</v>
       </c>
       <c r="E193" t="str">
         <v>PASSED</v>
@@ -3775,7 +3775,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D194">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="E194" t="str">
         <v>PASSED</v>
@@ -3792,7 +3792,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D195">
-        <v>1.49</v>
+        <v>0.23</v>
       </c>
       <c r="E195" t="str">
         <v>PASSED</v>
@@ -3809,7 +3809,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D196">
-        <v>1.28</v>
+        <v>2.12</v>
       </c>
       <c r="E196" t="str">
         <v>PASSED</v>
@@ -3826,7 +3826,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D197">
-        <v>0.15</v>
+        <v>1.23</v>
       </c>
       <c r="E197" t="str">
         <v>PASSED</v>
@@ -3843,7 +3843,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D198">
-        <v>0.79</v>
+        <v>1.62</v>
       </c>
       <c r="E198" t="str">
         <v>PASSED</v>
@@ -3860,7 +3860,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D199">
-        <v>0.56</v>
+        <v>0.22</v>
       </c>
       <c r="E199" t="str">
         <v>PASSED</v>
@@ -3877,7 +3877,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D200">
-        <v>2.33</v>
+        <v>0.83</v>
       </c>
       <c r="E200" t="str">
         <v>PASSED</v>
@@ -3894,7 +3894,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D201">
-        <v>0.89</v>
+        <v>1.21</v>
       </c>
       <c r="E201" t="str">
         <v>PASSED</v>
@@ -3911,7 +3911,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D202">
-        <v>0.12</v>
+        <v>1.87</v>
       </c>
       <c r="E202" t="str">
         <v>PASSED</v>
@@ -3928,7 +3928,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D203">
-        <v>0.97</v>
+        <v>0.34</v>
       </c>
       <c r="E203" t="str">
         <v>PASSED</v>
@@ -3945,7 +3945,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D204">
-        <v>1.87</v>
+        <v>0.62</v>
       </c>
       <c r="E204" t="str">
         <v>PASSED</v>
@@ -3962,7 +3962,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D205">
-        <v>0.45</v>
+        <v>2.06</v>
       </c>
       <c r="E205" t="str">
         <v>PASSED</v>
@@ -3979,7 +3979,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D206">
-        <v>1.7</v>
+        <v>0.32</v>
       </c>
       <c r="E206" t="str">
         <v>PASSED</v>
@@ -3996,7 +3996,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D207">
-        <v>1.88</v>
+        <v>1.39</v>
       </c>
       <c r="E207" t="str">
         <v>PASSED</v>
@@ -4013,7 +4013,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D208">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="E208" t="str">
         <v>PASSED</v>
@@ -4030,7 +4030,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D209">
-        <v>1.62</v>
+        <v>2.34</v>
       </c>
       <c r="E209" t="str">
         <v>PASSED</v>
@@ -4047,7 +4047,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D210">
-        <v>0.78</v>
+        <v>1.32</v>
       </c>
       <c r="E210" t="str">
         <v>PASSED</v>
@@ -4064,7 +4064,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D211">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="E211" t="str">
         <v>PASSED</v>
@@ -4081,7 +4081,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D212">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="E212" t="str">
         <v>PASSED</v>
@@ -4098,7 +4098,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D213">
-        <v>0.33</v>
+        <v>1.42</v>
       </c>
       <c r="E213" t="str">
         <v>PASSED</v>
@@ -4115,7 +4115,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D214">
-        <v>0.64</v>
+        <v>0.81</v>
       </c>
       <c r="E214" t="str">
         <v>PASSED</v>
@@ -4132,7 +4132,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D215">
-        <v>1.08</v>
+        <v>0.38</v>
       </c>
       <c r="E215" t="str">
         <v>PASSED</v>
@@ -4149,7 +4149,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D216">
-        <v>1.81</v>
+        <v>0.51</v>
       </c>
       <c r="E216" t="str">
         <v>PASSED</v>
@@ -4166,7 +4166,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D217">
-        <v>1.7</v>
+        <v>0.75</v>
       </c>
       <c r="E217" t="str">
         <v>PASSED</v>
@@ -4183,7 +4183,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D218">
-        <v>0.91</v>
+        <v>0.53</v>
       </c>
       <c r="E218" t="str">
         <v>PASSED</v>
@@ -4200,7 +4200,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D219">
-        <v>1.02</v>
+        <v>1.7</v>
       </c>
       <c r="E219" t="str">
         <v>PASSED</v>
@@ -4217,7 +4217,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D220">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="E220" t="str">
         <v>PASSED</v>
@@ -4234,7 +4234,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D221">
-        <v>1.97</v>
+        <v>0.65</v>
       </c>
       <c r="E221" t="str">
         <v>PASSED</v>
@@ -4251,7 +4251,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D222">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="E222" t="str">
         <v>PASSED</v>
@@ -4268,7 +4268,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D223">
-        <v>2.39</v>
+        <v>1.17</v>
       </c>
       <c r="E223" t="str">
         <v>PASSED</v>
@@ -4285,7 +4285,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D224">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="E224" t="str">
         <v>PASSED</v>
@@ -4302,7 +4302,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D225">
-        <v>1.89</v>
+        <v>1.45</v>
       </c>
       <c r="E225" t="str">
         <v>PASSED</v>
@@ -4319,7 +4319,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D226">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="E226" t="str">
         <v>PASSED</v>
@@ -4336,7 +4336,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D227">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="E227" t="str">
         <v>PASSED</v>
@@ -4353,7 +4353,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D228">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="E228" t="str">
         <v>PASSED</v>
@@ -4370,7 +4370,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D229">
-        <v>0.92</v>
+        <v>1.4</v>
       </c>
       <c r="E229" t="str">
         <v>PASSED</v>
@@ -4387,7 +4387,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D230">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="E230" t="str">
         <v>PASSED</v>
@@ -4404,7 +4404,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D231">
-        <v>2.21</v>
+        <v>1.18</v>
       </c>
       <c r="E231" t="str">
         <v>PASSED</v>
@@ -4421,7 +4421,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D232">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="E232" t="str">
         <v>PASSED</v>
@@ -4438,7 +4438,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D233">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="E233" t="str">
         <v>PASSED</v>
@@ -4455,7 +4455,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D234">
-        <v>2.31</v>
+        <v>0.67</v>
       </c>
       <c r="E234" t="str">
         <v>PASSED</v>
@@ -4472,7 +4472,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D235">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="E235" t="str">
         <v>PASSED</v>
@@ -4489,7 +4489,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D236">
-        <v>0.17</v>
+        <v>0.82</v>
       </c>
       <c r="E236" t="str">
         <v>PASSED</v>
@@ -4506,7 +4506,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D237">
-        <v>0.81</v>
+        <v>1.27</v>
       </c>
       <c r="E237" t="str">
         <v>PASSED</v>
@@ -4523,7 +4523,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D238">
-        <v>2.32</v>
+        <v>0.18</v>
       </c>
       <c r="E238" t="str">
         <v>PASSED</v>
@@ -4540,7 +4540,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D239">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="E239" t="str">
         <v>PASSED</v>
@@ -4557,7 +4557,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D240">
-        <v>1.96</v>
+        <v>1.02</v>
       </c>
       <c r="E240" t="str">
         <v>PASSED</v>
@@ -4574,7 +4574,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D241">
-        <v>0.13</v>
+        <v>2.3</v>
       </c>
       <c r="E241" t="str">
         <v>PASSED</v>
@@ -4591,7 +4591,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D242">
-        <v>0.89</v>
+        <v>2.44</v>
       </c>
       <c r="E242" t="str">
         <v>PASSED</v>
@@ -4608,7 +4608,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D243">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="E243" t="str">
         <v>PASSED</v>
@@ -4625,7 +4625,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D244">
-        <v>0.31</v>
+        <v>1.34</v>
       </c>
       <c r="E244" t="str">
         <v>PASSED</v>
@@ -4642,7 +4642,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D245">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="E245" t="str">
         <v>PASSED</v>
@@ -4659,7 +4659,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D246">
-        <v>0.22</v>
+        <v>1.99</v>
       </c>
       <c r="E246" t="str">
         <v>PASSED</v>
@@ -4676,7 +4676,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D247">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="E247" t="str">
         <v>PASSED</v>
@@ -4693,7 +4693,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D248">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="E248" t="str">
         <v>PASSED</v>
@@ -4710,7 +4710,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D249">
-        <v>0.26</v>
+        <v>1.44</v>
       </c>
       <c r="E249" t="str">
         <v>PASSED</v>
@@ -4727,7 +4727,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D250">
-        <v>0.56</v>
+        <v>0.1</v>
       </c>
       <c r="E250" t="str">
         <v>PASSED</v>
@@ -4744,7 +4744,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D251">
-        <v>0.85</v>
+        <v>1.19</v>
       </c>
       <c r="E251" t="str">
         <v>PASSED</v>
@@ -4761,7 +4761,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D252">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="E252" t="str">
         <v>PASSED</v>
@@ -4778,7 +4778,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D253">
-        <v>1.81</v>
+        <v>1.03</v>
       </c>
       <c r="E253" t="str">
         <v>PASSED</v>
@@ -4795,7 +4795,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D254">
-        <v>0.85</v>
+        <v>0.33</v>
       </c>
       <c r="E254" t="str">
         <v>PASSED</v>
@@ -4812,7 +4812,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D255">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="E255" t="str">
         <v>PASSED</v>
@@ -4829,7 +4829,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D256">
-        <v>0.61</v>
+        <v>0.12</v>
       </c>
       <c r="E256" t="str">
         <v>PASSED</v>
@@ -4846,7 +4846,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D257">
-        <v>1.54</v>
+        <v>2.12</v>
       </c>
       <c r="E257" t="str">
         <v>PASSED</v>
@@ -4863,7 +4863,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D258">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="E258" t="str">
         <v>PASSED</v>
@@ -4880,7 +4880,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D259">
-        <v>0.16</v>
+        <v>1.82</v>
       </c>
       <c r="E259" t="str">
         <v>PASSED</v>
@@ -4897,7 +4897,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D260">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="E260" t="str">
         <v>PASSED</v>
@@ -4914,7 +4914,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D261">
-        <v>2.28</v>
+        <v>0.21</v>
       </c>
       <c r="E261" t="str">
         <v>PASSED</v>
@@ -4931,7 +4931,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D262">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="E262" t="str">
         <v>PASSED</v>
@@ -4948,7 +4948,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D263">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="E263" t="str">
         <v>PASSED</v>
@@ -4965,7 +4965,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D264">
-        <v>0.32</v>
+        <v>2.04</v>
       </c>
       <c r="E264" t="str">
         <v>PASSED</v>
@@ -4982,7 +4982,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D265">
-        <v>0.52</v>
+        <v>2.49</v>
       </c>
       <c r="E265" t="str">
         <v>PASSED</v>
@@ -4999,7 +4999,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D266">
-        <v>1.87</v>
+        <v>0.74</v>
       </c>
       <c r="E266" t="str">
         <v>PASSED</v>
@@ -5016,7 +5016,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D267">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="E267" t="str">
         <v>PASSED</v>
@@ -5033,7 +5033,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D268">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="E268" t="str">
         <v>PASSED</v>
@@ -5050,7 +5050,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D269">
-        <v>1.79</v>
+        <v>1.31</v>
       </c>
       <c r="E269" t="str">
         <v>PASSED</v>
@@ -5067,7 +5067,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D270">
-        <v>1.11</v>
+        <v>0.23</v>
       </c>
       <c r="E270" t="str">
         <v>PASSED</v>
@@ -5084,7 +5084,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D271">
-        <v>0.37</v>
+        <v>0.28</v>
       </c>
       <c r="E271" t="str">
         <v>PASSED</v>
@@ -5101,7 +5101,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D272">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="E272" t="str">
         <v>PASSED</v>
@@ -5118,7 +5118,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D273">
-        <v>2.14</v>
+        <v>0.77</v>
       </c>
       <c r="E273" t="str">
         <v>PASSED</v>
@@ -5135,7 +5135,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D274">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="E274" t="str">
         <v>PASSED</v>
@@ -5152,7 +5152,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D275">
-        <v>2.43</v>
+        <v>0.39</v>
       </c>
       <c r="E275" t="str">
         <v>PASSED</v>
@@ -5169,7 +5169,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D276">
-        <v>1.09</v>
+        <v>0.44</v>
       </c>
       <c r="E276" t="str">
         <v>PASSED</v>
@@ -5186,7 +5186,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D277">
-        <v>0.38</v>
+        <v>2.46</v>
       </c>
       <c r="E277" t="str">
         <v>PASSED</v>
@@ -5203,7 +5203,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D278">
-        <v>1.51</v>
+        <v>2.3</v>
       </c>
       <c r="E278" t="str">
         <v>PASSED</v>
@@ -5220,7 +5220,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D279">
-        <v>0.56</v>
+        <v>1.73</v>
       </c>
       <c r="E279" t="str">
         <v>PASSED</v>
@@ -5237,7 +5237,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D280">
-        <v>2.28</v>
+        <v>0.73</v>
       </c>
       <c r="E280" t="str">
         <v>PASSED</v>
@@ -5254,7 +5254,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D281">
-        <v>1.8</v>
+        <v>0.25</v>
       </c>
       <c r="E281" t="str">
         <v>PASSED</v>
@@ -5271,7 +5271,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D282">
-        <v>0.72</v>
+        <v>1.38</v>
       </c>
       <c r="E282" t="str">
         <v>PASSED</v>
@@ -5288,7 +5288,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D283">
-        <v>0.19</v>
+        <v>2.19</v>
       </c>
       <c r="E283" t="str">
         <v>PASSED</v>
@@ -5305,7 +5305,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D284">
-        <v>1.86</v>
+        <v>0.51</v>
       </c>
       <c r="E284" t="str">
         <v>PASSED</v>
@@ -5322,7 +5322,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D285">
-        <v>1.69</v>
+        <v>0.89</v>
       </c>
       <c r="E285" t="str">
         <v>PASSED</v>
@@ -5339,7 +5339,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D286">
-        <v>0.9</v>
+        <v>1.79</v>
       </c>
       <c r="E286" t="str">
         <v>PASSED</v>
@@ -5356,7 +5356,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D287">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="E287" t="str">
         <v>PASSED</v>
@@ -5373,7 +5373,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D288">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="E288" t="str">
         <v>PASSED</v>
@@ -5390,7 +5390,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D289">
-        <v>0.95</v>
+        <v>0.41</v>
       </c>
       <c r="E289" t="str">
         <v>PASSED</v>
@@ -5407,7 +5407,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D290">
-        <v>0.46</v>
+        <v>1.09</v>
       </c>
       <c r="E290" t="str">
         <v>PASSED</v>
@@ -5424,7 +5424,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D291">
-        <v>1.61</v>
+        <v>0.41</v>
       </c>
       <c r="E291" t="str">
         <v>PASSED</v>
@@ -5441,7 +5441,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D292">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="E292" t="str">
         <v>PASSED</v>
@@ -5458,7 +5458,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D293">
-        <v>0.77</v>
+        <v>0.48</v>
       </c>
       <c r="E293" t="str">
         <v>PASSED</v>
@@ -5492,7 +5492,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D295">
-        <v>0.18</v>
+        <v>1.76</v>
       </c>
       <c r="E295" t="str">
         <v>PASSED</v>
@@ -5509,7 +5509,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D296">
-        <v>0.22</v>
+        <v>2.17</v>
       </c>
       <c r="E296" t="str">
         <v>PASSED</v>
@@ -5526,7 +5526,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D297">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="E297" t="str">
         <v>PASSED</v>
@@ -5543,7 +5543,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D298">
-        <v>0.31</v>
+        <v>1.08</v>
       </c>
       <c r="E298" t="str">
         <v>PASSED</v>
@@ -5560,7 +5560,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D299">
-        <v>0.99</v>
+        <v>1.74</v>
       </c>
       <c r="E299" t="str">
         <v>PASSED</v>
@@ -5577,7 +5577,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D300">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="E300" t="str">
         <v>PASSED</v>
@@ -5594,7 +5594,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D301">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E301" t="str">
         <v>PASSED</v>
@@ -5611,7 +5611,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D302">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="E302" t="str">
         <v>PASSED</v>
@@ -5628,7 +5628,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D303">
-        <v>0.4</v>
+        <v>1.91</v>
       </c>
       <c r="E303" t="str">
         <v>PASSED</v>
@@ -5645,7 +5645,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D304">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="E304" t="str">
         <v>PASSED</v>
@@ -5662,7 +5662,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D305">
-        <v>1.91</v>
+        <v>0.29</v>
       </c>
       <c r="E305" t="str">
         <v>PASSED</v>
@@ -5679,7 +5679,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D306">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="E306" t="str">
         <v>PASSED</v>
@@ -5696,7 +5696,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D307">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="E307" t="str">
         <v>PASSED</v>
@@ -5713,7 +5713,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D308">
-        <v>0.52</v>
+        <v>0.21</v>
       </c>
       <c r="E308" t="str">
         <v>PASSED</v>
@@ -5730,7 +5730,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D309">
-        <v>0.36</v>
+        <v>1.67</v>
       </c>
       <c r="E309" t="str">
         <v>PASSED</v>
@@ -5747,7 +5747,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D310">
-        <v>1.17</v>
+        <v>1.93</v>
       </c>
       <c r="E310" t="str">
         <v>PASSED</v>
@@ -5764,7 +5764,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D311">
-        <v>0.28</v>
+        <v>1.9</v>
       </c>
       <c r="E311" t="str">
         <v>PASSED</v>
@@ -5781,7 +5781,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D312">
-        <v>0.57</v>
+        <v>1.24</v>
       </c>
       <c r="E312" t="str">
         <v>PASSED</v>
@@ -5798,7 +5798,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D313">
-        <v>2.06</v>
+        <v>0.5</v>
       </c>
       <c r="E313" t="str">
         <v>PASSED</v>
@@ -5815,7 +5815,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D314">
-        <v>2.2</v>
+        <v>0.55</v>
       </c>
       <c r="E314" t="str">
         <v>PASSED</v>
@@ -5832,7 +5832,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D315">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="E315" t="str">
         <v>PASSED</v>
@@ -5849,7 +5849,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D316">
-        <v>2.18</v>
+        <v>0.62</v>
       </c>
       <c r="E316" t="str">
         <v>PASSED</v>
@@ -5866,7 +5866,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D317">
-        <v>1.66</v>
+        <v>2.47</v>
       </c>
       <c r="E317" t="str">
         <v>PASSED</v>
@@ -5883,7 +5883,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D318">
-        <v>1.64</v>
+        <v>1.07</v>
       </c>
       <c r="E318" t="str">
         <v>PASSED</v>
@@ -5900,7 +5900,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D319">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="E319" t="str">
         <v>PASSED</v>
@@ -5917,7 +5917,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D320">
-        <v>0.25</v>
+        <v>0.63</v>
       </c>
       <c r="E320" t="str">
         <v>PASSED</v>
@@ -5934,7 +5934,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D321">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="E321" t="str">
         <v>PASSED</v>
@@ -5951,7 +5951,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D322">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="E322" t="str">
         <v>PASSED</v>
@@ -5985,7 +5985,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D324">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="E324" t="str">
         <v>PASSED</v>
@@ -6002,7 +6002,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D325">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="E325" t="str">
         <v>PASSED</v>
@@ -6019,7 +6019,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D326">
-        <v>1.61</v>
+        <v>2.08</v>
       </c>
       <c r="E326" t="str">
         <v>PASSED</v>
@@ -6036,7 +6036,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D327">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="E327" t="str">
         <v>PASSED</v>
@@ -6053,7 +6053,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D328">
-        <v>1.75</v>
+        <v>0.76</v>
       </c>
       <c r="E328" t="str">
         <v>PASSED</v>
@@ -6070,7 +6070,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D329">
-        <v>1.33</v>
+        <v>0.64</v>
       </c>
       <c r="E329" t="str">
         <v>PASSED</v>
@@ -6087,7 +6087,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D330">
-        <v>1.03</v>
+        <v>0.52</v>
       </c>
       <c r="E330" t="str">
         <v>PASSED</v>
@@ -6104,7 +6104,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D331">
-        <v>0.12</v>
+        <v>1.97</v>
       </c>
       <c r="E331" t="str">
         <v>PASSED</v>
@@ -6121,7 +6121,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D332">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="E332" t="str">
         <v>PASSED</v>
@@ -6138,7 +6138,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D333">
-        <v>0.94</v>
+        <v>0.58</v>
       </c>
       <c r="E333" t="str">
         <v>PASSED</v>
@@ -6155,7 +6155,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D334">
-        <v>0.23</v>
+        <v>0.88</v>
       </c>
       <c r="E334" t="str">
         <v>PASSED</v>
@@ -6172,7 +6172,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D335">
-        <v>0.1</v>
+        <v>2.39</v>
       </c>
       <c r="E335" t="str">
         <v>PASSED</v>
@@ -6189,7 +6189,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D336">
-        <v>2.31</v>
+        <v>1.46</v>
       </c>
       <c r="E336" t="str">
         <v>PASSED</v>
@@ -6206,7 +6206,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D337">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="E337" t="str">
         <v>PASSED</v>
@@ -6223,7 +6223,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D338">
-        <v>0.52</v>
+        <v>2.39</v>
       </c>
       <c r="E338" t="str">
         <v>PASSED</v>
@@ -6240,7 +6240,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D339">
-        <v>1.12</v>
+        <v>1.85</v>
       </c>
       <c r="E339" t="str">
         <v>PASSED</v>
@@ -6257,7 +6257,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D340">
-        <v>0.34</v>
+        <v>1.14</v>
       </c>
       <c r="E340" t="str">
         <v>PASSED</v>
@@ -6274,7 +6274,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D341">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="E341" t="str">
         <v>PASSED</v>
@@ -6291,7 +6291,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D342">
-        <v>0.57</v>
+        <v>1.92</v>
       </c>
       <c r="E342" t="str">
         <v>PASSED</v>
@@ -6308,7 +6308,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D343">
-        <v>1.97</v>
+        <v>0.77</v>
       </c>
       <c r="E343" t="str">
         <v>PASSED</v>
@@ -6325,7 +6325,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D344">
-        <v>2.03</v>
+        <v>1.68</v>
       </c>
       <c r="E344" t="str">
         <v>PASSED</v>
@@ -6342,7 +6342,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D345">
-        <v>2.49</v>
+        <v>0.55</v>
       </c>
       <c r="E345" t="str">
         <v>PASSED</v>
@@ -6359,7 +6359,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D346">
-        <v>0.68</v>
+        <v>2.07</v>
       </c>
       <c r="E346" t="str">
         <v>PASSED</v>
@@ -6376,7 +6376,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D347">
-        <v>0.66</v>
+        <v>2.34</v>
       </c>
       <c r="E347" t="str">
         <v>PASSED</v>
@@ -6393,7 +6393,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D348">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="E348" t="str">
         <v>PASSED</v>
@@ -6410,7 +6410,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D349">
-        <v>1.58</v>
+        <v>0.27</v>
       </c>
       <c r="E349" t="str">
         <v>PASSED</v>
@@ -6427,7 +6427,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D350">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="E350" t="str">
         <v>PASSED</v>
@@ -6444,7 +6444,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D351">
-        <v>0.93</v>
+        <v>1.29</v>
       </c>
       <c r="E351" t="str">
         <v>PASSED</v>
@@ -6461,7 +6461,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D352">
-        <v>1.83</v>
+        <v>1.06</v>
       </c>
       <c r="E352" t="str">
         <v>PASSED</v>
@@ -6478,7 +6478,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D353">
-        <v>1.71</v>
+        <v>0.8</v>
       </c>
       <c r="E353" t="str">
         <v>PASSED</v>
@@ -6495,7 +6495,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D354">
-        <v>0.18</v>
+        <v>1.64</v>
       </c>
       <c r="E354" t="str">
         <v>PASSED</v>
@@ -6512,7 +6512,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D355">
-        <v>1.66</v>
+        <v>0.46</v>
       </c>
       <c r="E355" t="str">
         <v>PASSED</v>
@@ -6529,7 +6529,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D356">
-        <v>0.62</v>
+        <v>2.02</v>
       </c>
       <c r="E356" t="str">
         <v>PASSED</v>
@@ -6546,7 +6546,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D357">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="E357" t="str">
         <v>PASSED</v>
@@ -6563,7 +6563,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D358">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="E358" t="str">
         <v>PASSED</v>
@@ -6580,7 +6580,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D359">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="E359" t="str">
         <v>PASSED</v>
@@ -6614,7 +6614,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D361">
-        <v>1.25</v>
+        <v>0.79</v>
       </c>
       <c r="E361" t="str">
         <v>PASSED</v>
@@ -6631,7 +6631,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D362">
-        <v>2.07</v>
+        <v>0.61</v>
       </c>
       <c r="E362" t="str">
         <v>PASSED</v>
@@ -6648,7 +6648,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D363">
-        <v>1.02</v>
+        <v>0.64</v>
       </c>
       <c r="E363" t="str">
         <v>PASSED</v>
@@ -6665,7 +6665,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D364">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="E364" t="str">
         <v>PASSED</v>
@@ -6682,7 +6682,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D365">
-        <v>0.49</v>
+        <v>1.06</v>
       </c>
       <c r="E365" t="str">
         <v>PASSED</v>
@@ -6699,7 +6699,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D366">
-        <v>0.3</v>
+        <v>2.03</v>
       </c>
       <c r="E366" t="str">
         <v>PASSED</v>
@@ -6716,7 +6716,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D367">
-        <v>2.03</v>
+        <v>1.06</v>
       </c>
       <c r="E367" t="str">
         <v>PASSED</v>
@@ -6733,7 +6733,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D368">
-        <v>1</v>
+        <v>2.06</v>
       </c>
       <c r="E368" t="str">
         <v>PASSED</v>
@@ -6750,7 +6750,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D369">
-        <v>1.6</v>
+        <v>0.25</v>
       </c>
       <c r="E369" t="str">
         <v>PASSED</v>
@@ -6767,7 +6767,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D370">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E370" t="str">
         <v>PASSED</v>
@@ -6784,7 +6784,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D371">
-        <v>1.93</v>
+        <v>0.56</v>
       </c>
       <c r="E371" t="str">
         <v>PASSED</v>
@@ -6801,7 +6801,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D372">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="E372" t="str">
         <v>PASSED</v>
@@ -6818,7 +6818,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D373">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="E373" t="str">
         <v>PASSED</v>
@@ -6835,7 +6835,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D374">
-        <v>0.47</v>
+        <v>0.15</v>
       </c>
       <c r="E374" t="str">
         <v>PASSED</v>
@@ -6852,7 +6852,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D375">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="E375" t="str">
         <v>PASSED</v>
@@ -6869,7 +6869,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D376">
-        <v>0.53</v>
+        <v>0.18</v>
       </c>
       <c r="E376" t="str">
         <v>PASSED</v>
@@ -6886,7 +6886,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D377">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="E377" t="str">
         <v>PASSED</v>
@@ -6903,7 +6903,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D378">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="E378" t="str">
         <v>PASSED</v>
@@ -6920,7 +6920,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D379">
-        <v>2.3</v>
+        <v>1.08</v>
       </c>
       <c r="E379" t="str">
         <v>PASSED</v>
@@ -6937,7 +6937,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D380">
-        <v>0.33</v>
+        <v>2.15</v>
       </c>
       <c r="E380" t="str">
         <v>PASSED</v>
@@ -6954,7 +6954,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D381">
-        <v>0.52</v>
+        <v>1.72</v>
       </c>
       <c r="E381" t="str">
         <v>PASSED</v>
@@ -6971,7 +6971,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D382">
-        <v>2.18</v>
+        <v>0.15</v>
       </c>
       <c r="E382" t="str">
         <v>PASSED</v>
@@ -6988,7 +6988,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D383">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="E383" t="str">
         <v>PASSED</v>
@@ -7005,7 +7005,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D384">
-        <v>0.79</v>
+        <v>1.96</v>
       </c>
       <c r="E384" t="str">
         <v>PASSED</v>
@@ -7022,7 +7022,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D385">
-        <v>1.96</v>
+        <v>0.39</v>
       </c>
       <c r="E385" t="str">
         <v>PASSED</v>
@@ -7039,7 +7039,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D386">
-        <v>1.92</v>
+        <v>2.48</v>
       </c>
       <c r="E386" t="str">
         <v>PASSED</v>
@@ -7056,7 +7056,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D387">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="E387" t="str">
         <v>PASSED</v>
@@ -7073,7 +7073,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D388">
-        <v>1.83</v>
+        <v>0.37</v>
       </c>
       <c r="E388" t="str">
         <v>PASSED</v>
@@ -7090,7 +7090,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D389">
-        <v>0.17</v>
+        <v>1.21</v>
       </c>
       <c r="E389" t="str">
         <v>PASSED</v>
@@ -7107,7 +7107,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D390">
-        <v>1.12</v>
+        <v>1.62</v>
       </c>
       <c r="E390" t="str">
         <v>PASSED</v>
@@ -7124,7 +7124,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D391">
-        <v>1.59</v>
+        <v>0.85</v>
       </c>
       <c r="E391" t="str">
         <v>PASSED</v>
@@ -7141,7 +7141,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D392">
-        <v>0.59</v>
+        <v>1.54</v>
       </c>
       <c r="E392" t="str">
         <v>PASSED</v>
@@ -7158,7 +7158,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D393">
-        <v>0.34</v>
+        <v>1.22</v>
       </c>
       <c r="E393" t="str">
         <v>PASSED</v>
@@ -7175,7 +7175,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D394">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="E394" t="str">
         <v>PASSED</v>
@@ -7192,7 +7192,7 @@
         <v>Verify load stability on /api/auth/register</v>
       </c>
       <c r="D395">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="E395" t="str">
         <v>PASSED</v>
@@ -7209,7 +7209,7 @@
         <v>Verify load stability on /api/bookings</v>
       </c>
       <c r="D396">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="E396" t="str">
         <v>PASSED</v>
@@ -7226,7 +7226,7 @@
         <v>Verify load stability on /api/bookings/my</v>
       </c>
       <c r="D397">
-        <v>2.22</v>
+        <v>0.92</v>
       </c>
       <c r="E397" t="str">
         <v>PASSED</v>
@@ -7243,7 +7243,7 @@
         <v>Verify load stability on /api/bookings/match</v>
       </c>
       <c r="D398">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="E398" t="str">
         <v>PASSED</v>
@@ -7260,7 +7260,7 @@
         <v>Verify load stability on /api/admin/users</v>
       </c>
       <c r="D399">
-        <v>0.99</v>
+        <v>2.07</v>
       </c>
       <c r="E399" t="str">
         <v>PASSED</v>
@@ -7277,7 +7277,7 @@
         <v>Verify load stability on /api/health</v>
       </c>
       <c r="D400">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="E400" t="str">
         <v>PASSED</v>
@@ -7294,7 +7294,7 @@
         <v>Verify load stability on /api/auth/login</v>
       </c>
       <c r="D401">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="E401" t="str">
         <v>PASSED</v>
@@ -7388,1129 +7388,1129 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-06-23 05:13:23</v>
+        <v>2026-06-23 05:24:45</v>
       </c>
       <c r="B2" t="str">
         <v>INFO</v>
       </c>
       <c r="C2" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.99s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.78s</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-06-23 05:13:24</v>
+        <v>2026-06-23 05:24:46</v>
       </c>
       <c r="B3" t="str">
         <v>INFO</v>
       </c>
       <c r="C3" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.10s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.25s</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-23 05:13:25</v>
+        <v>2026-06-23 05:24:47</v>
       </c>
       <c r="B4" t="str">
         <v>INFO</v>
       </c>
       <c r="C4" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.50s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.57s</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-06-23 05:13:26</v>
+        <v>2026-06-23 05:24:48</v>
       </c>
       <c r="B5" t="str">
         <v>INFO</v>
       </c>
       <c r="C5" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.37s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.65s</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-06-23 05:13:27</v>
+        <v>2026-06-23 05:24:49</v>
       </c>
       <c r="B6" t="str">
         <v>INFO</v>
       </c>
       <c r="C6" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.30s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.72s</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-06-23 05:13:28</v>
+        <v>2026-06-23 05:24:50</v>
       </c>
       <c r="B7" t="str">
         <v>INFO</v>
       </c>
       <c r="C7" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.75s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.79s</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-06-23 05:13:29</v>
+        <v>2026-06-23 05:24:51</v>
       </c>
       <c r="B8" t="str">
         <v>INFO</v>
       </c>
       <c r="C8" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.59s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.53s</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-06-23 05:13:30</v>
+        <v>2026-06-23 05:24:52</v>
       </c>
       <c r="B9" t="str">
         <v>INFO</v>
       </c>
       <c r="C9" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.91s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.64s</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-06-23 05:13:31</v>
+        <v>2026-06-23 05:24:53</v>
       </c>
       <c r="B10" t="str">
         <v>INFO</v>
       </c>
       <c r="C10" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.77s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.15s</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-06-23 05:13:32</v>
+        <v>2026-06-23 05:24:54</v>
       </c>
       <c r="B11" t="str">
         <v>INFO</v>
       </c>
       <c r="C11" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.52s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.18s</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-06-23 05:13:33</v>
+        <v>2026-06-23 05:24:55</v>
       </c>
       <c r="B12" t="str">
         <v>INFO</v>
       </c>
       <c r="C12" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.37s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.12s</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-06-23 05:13:34</v>
+        <v>2026-06-23 05:24:56</v>
       </c>
       <c r="B13" t="str">
         <v>INFO</v>
       </c>
       <c r="C13" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.09s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.84s</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-06-23 05:13:35</v>
+        <v>2026-06-23 05:24:57</v>
       </c>
       <c r="B14" t="str">
         <v>INFO</v>
       </c>
       <c r="C14" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.21s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.35s</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-06-23 05:13:36</v>
+        <v>2026-06-23 05:24:58</v>
       </c>
       <c r="B15" t="str">
         <v>INFO</v>
       </c>
       <c r="C15" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.00s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.17s</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-06-23 05:13:37</v>
+        <v>2026-06-23 05:24:59</v>
       </c>
       <c r="B16" t="str">
         <v>INFO</v>
       </c>
       <c r="C16" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.36s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.05s</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-06-23 05:13:38</v>
+        <v>2026-06-23 05:25:00</v>
       </c>
       <c r="B17" t="str">
         <v>INFO</v>
       </c>
       <c r="C17" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.70s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.14s</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-06-23 05:13:39</v>
+        <v>2026-06-23 05:25:01</v>
       </c>
       <c r="B18" t="str">
         <v>INFO</v>
       </c>
       <c r="C18" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.40s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.37s</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-06-23 05:13:40</v>
+        <v>2026-06-23 05:25:02</v>
       </c>
       <c r="B19" t="str">
         <v>INFO</v>
       </c>
       <c r="C19" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.70s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.81s</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-06-23 05:13:41</v>
+        <v>2026-06-23 05:25:03</v>
       </c>
       <c r="B20" t="str">
         <v>INFO</v>
       </c>
       <c r="C20" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.73s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.53s</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-06-23 05:13:42</v>
+        <v>2026-06-23 05:25:04</v>
       </c>
       <c r="B21" t="str">
         <v>INFO</v>
       </c>
       <c r="C21" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.99s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.07s</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-06-23 05:13:43</v>
+        <v>2026-06-23 05:25:05</v>
       </c>
       <c r="B22" t="str">
         <v>INFO</v>
       </c>
       <c r="C22" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.02s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.43s</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-06-23 05:13:44</v>
+        <v>2026-06-23 05:25:06</v>
       </c>
       <c r="B23" t="str">
         <v>INFO</v>
       </c>
       <c r="C23" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.44s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.94s</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-06-23 05:13:45</v>
+        <v>2026-06-23 05:25:07</v>
       </c>
       <c r="B24" t="str">
         <v>INFO</v>
       </c>
       <c r="C24" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.43s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.11s</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-06-23 05:13:46</v>
+        <v>2026-06-23 05:25:08</v>
       </c>
       <c r="B25" t="str">
         <v>INFO</v>
       </c>
       <c r="C25" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.21s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.35s</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-06-23 05:13:47</v>
+        <v>2026-06-23 05:25:09</v>
       </c>
       <c r="B26" t="str">
         <v>INFO</v>
       </c>
       <c r="C26" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.61s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.40s</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-06-23 05:13:48</v>
+        <v>2026-06-23 05:25:10</v>
       </c>
       <c r="B27" t="str">
         <v>INFO</v>
       </c>
       <c r="C27" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.26s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.18s</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-06-23 05:13:49</v>
+        <v>2026-06-23 05:25:11</v>
       </c>
       <c r="B28" t="str">
         <v>INFO</v>
       </c>
       <c r="C28" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.72s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.23s</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-06-23 05:13:50</v>
+        <v>2026-06-23 05:25:12</v>
       </c>
       <c r="B29" t="str">
         <v>INFO</v>
       </c>
       <c r="C29" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.64s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.16s</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-06-23 05:13:51</v>
+        <v>2026-06-23 05:25:13</v>
       </c>
       <c r="B30" t="str">
         <v>INFO</v>
       </c>
       <c r="C30" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.86s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.08s</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-06-23 05:13:52</v>
+        <v>2026-06-23 05:25:14</v>
       </c>
       <c r="B31" t="str">
         <v>INFO</v>
       </c>
       <c r="C31" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.52s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.33s</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-06-23 05:13:53</v>
+        <v>2026-06-23 05:25:15</v>
       </c>
       <c r="B32" t="str">
         <v>INFO</v>
       </c>
       <c r="C32" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.67s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.98s</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-06-23 05:13:54</v>
+        <v>2026-06-23 05:25:16</v>
       </c>
       <c r="B33" t="str">
         <v>INFO</v>
       </c>
       <c r="C33" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.20s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.34s</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-06-23 05:13:55</v>
+        <v>2026-06-23 05:25:17</v>
       </c>
       <c r="B34" t="str">
         <v>INFO</v>
       </c>
       <c r="C34" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.45s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.94s</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-06-23 05:13:56</v>
+        <v>2026-06-23 05:25:18</v>
       </c>
       <c r="B35" t="str">
         <v>INFO</v>
       </c>
       <c r="C35" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.19s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.41s</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-06-23 05:13:57</v>
+        <v>2026-06-23 05:25:19</v>
       </c>
       <c r="B36" t="str">
         <v>INFO</v>
       </c>
       <c r="C36" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.95s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.52s</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-06-23 05:13:58</v>
+        <v>2026-06-23 05:25:20</v>
       </c>
       <c r="B37" t="str">
         <v>INFO</v>
       </c>
       <c r="C37" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.42s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.89s</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-06-23 05:13:59</v>
+        <v>2026-06-23 05:25:21</v>
       </c>
       <c r="B38" t="str">
         <v>INFO</v>
       </c>
       <c r="C38" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.74s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.60s</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-06-23 05:14:00</v>
+        <v>2026-06-23 05:25:22</v>
       </c>
       <c r="B39" t="str">
         <v>INFO</v>
       </c>
       <c r="C39" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.99s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.13s</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-06-23 05:14:01</v>
+        <v>2026-06-23 05:25:23</v>
       </c>
       <c r="B40" t="str">
         <v>INFO</v>
       </c>
       <c r="C40" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.43s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.04s</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-06-23 05:14:02</v>
+        <v>2026-06-23 05:25:24</v>
       </c>
       <c r="B41" t="str">
         <v>INFO</v>
       </c>
       <c r="C41" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.70s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.27s</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-06-23 05:14:03</v>
+        <v>2026-06-23 05:25:25</v>
       </c>
       <c r="B42" t="str">
         <v>INFO</v>
       </c>
       <c r="C42" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.30s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.88s</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-06-23 05:14:04</v>
+        <v>2026-06-23 05:25:26</v>
       </c>
       <c r="B43" t="str">
         <v>INFO</v>
       </c>
       <c r="C43" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.25s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.45s</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-06-23 05:14:05</v>
+        <v>2026-06-23 05:25:27</v>
       </c>
       <c r="B44" t="str">
         <v>INFO</v>
       </c>
       <c r="C44" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.85s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.66s</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-06-23 05:14:06</v>
+        <v>2026-06-23 05:25:28</v>
       </c>
       <c r="B45" t="str">
         <v>INFO</v>
       </c>
       <c r="C45" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.13s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.68s</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-06-23 05:14:07</v>
+        <v>2026-06-23 05:25:29</v>
       </c>
       <c r="B46" t="str">
         <v>INFO</v>
       </c>
       <c r="C46" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.30s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.78s</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-06-23 05:14:08</v>
+        <v>2026-06-23 05:25:30</v>
       </c>
       <c r="B47" t="str">
         <v>INFO</v>
       </c>
       <c r="C47" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.00s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.58s</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-06-23 05:14:09</v>
+        <v>2026-06-23 05:25:31</v>
       </c>
       <c r="B48" t="str">
         <v>INFO</v>
       </c>
       <c r="C48" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.09s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.98s</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-06-23 05:14:10</v>
+        <v>2026-06-23 05:25:32</v>
       </c>
       <c r="B49" t="str">
         <v>INFO</v>
       </c>
       <c r="C49" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.94s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.29s</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-06-23 05:14:11</v>
+        <v>2026-06-23 05:25:33</v>
       </c>
       <c r="B50" t="str">
         <v>INFO</v>
       </c>
       <c r="C50" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.06s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.26s</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-06-23 05:14:12</v>
+        <v>2026-06-23 05:25:34</v>
       </c>
       <c r="B51" t="str">
         <v>INFO</v>
       </c>
       <c r="C51" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.26s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.36s</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-06-23 05:14:13</v>
+        <v>2026-06-23 05:25:35</v>
       </c>
       <c r="B52" t="str">
         <v>INFO</v>
       </c>
       <c r="C52" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.05s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.26s</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-06-23 05:14:14</v>
+        <v>2026-06-23 05:25:36</v>
       </c>
       <c r="B53" t="str">
         <v>INFO</v>
       </c>
       <c r="C53" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.87s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.50s</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-06-23 05:14:15</v>
+        <v>2026-06-23 05:25:37</v>
       </c>
       <c r="B54" t="str">
         <v>INFO</v>
       </c>
       <c r="C54" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.96s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.44s</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-06-23 05:14:16</v>
+        <v>2026-06-23 05:25:38</v>
       </c>
       <c r="B55" t="str">
         <v>INFO</v>
       </c>
       <c r="C55" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.68s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.72s</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-06-23 05:14:17</v>
+        <v>2026-06-23 05:25:39</v>
       </c>
       <c r="B56" t="str">
         <v>INFO</v>
       </c>
       <c r="C56" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.37s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.05s</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-06-23 05:14:18</v>
+        <v>2026-06-23 05:25:40</v>
       </c>
       <c r="B57" t="str">
         <v>INFO</v>
       </c>
       <c r="C57" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.06s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.81s</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-06-23 05:14:19</v>
+        <v>2026-06-23 05:25:41</v>
       </c>
       <c r="B58" t="str">
         <v>INFO</v>
       </c>
       <c r="C58" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.60s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.72s</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-06-23 05:14:20</v>
+        <v>2026-06-23 05:25:42</v>
       </c>
       <c r="B59" t="str">
         <v>INFO</v>
       </c>
       <c r="C59" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.44s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.58s</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-06-23 05:14:21</v>
+        <v>2026-06-23 05:25:43</v>
       </c>
       <c r="B60" t="str">
         <v>INFO</v>
       </c>
       <c r="C60" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.02s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.82s</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-06-23 05:14:22</v>
+        <v>2026-06-23 05:25:44</v>
       </c>
       <c r="B61" t="str">
         <v>INFO</v>
       </c>
       <c r="C61" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.13s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.52s</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-06-23 05:14:23</v>
+        <v>2026-06-23 05:25:45</v>
       </c>
       <c r="B62" t="str">
         <v>INFO</v>
       </c>
       <c r="C62" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.64s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.94s</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-06-23 05:14:24</v>
+        <v>2026-06-23 05:25:46</v>
       </c>
       <c r="B63" t="str">
         <v>INFO</v>
       </c>
       <c r="C63" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.63s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.26s</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-06-23 05:14:25</v>
+        <v>2026-06-23 05:25:47</v>
       </c>
       <c r="B64" t="str">
         <v>INFO</v>
       </c>
       <c r="C64" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.97s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.17s</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-06-23 05:14:26</v>
+        <v>2026-06-23 05:25:48</v>
       </c>
       <c r="B65" t="str">
         <v>INFO</v>
       </c>
       <c r="C65" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.03s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.19s</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-06-23 05:14:27</v>
+        <v>2026-06-23 05:25:49</v>
       </c>
       <c r="B66" t="str">
         <v>INFO</v>
       </c>
       <c r="C66" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.36s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.50s</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-06-23 05:14:28</v>
+        <v>2026-06-23 05:25:50</v>
       </c>
       <c r="B67" t="str">
         <v>INFO</v>
       </c>
       <c r="C67" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.19s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.51s</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-06-23 05:14:29</v>
+        <v>2026-06-23 05:25:51</v>
       </c>
       <c r="B68" t="str">
         <v>INFO</v>
       </c>
       <c r="C68" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.34s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.56s</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-06-23 05:14:30</v>
+        <v>2026-06-23 05:25:52</v>
       </c>
       <c r="B69" t="str">
         <v>INFO</v>
       </c>
       <c r="C69" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.98s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.03s</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-06-23 05:14:31</v>
+        <v>2026-06-23 05:25:53</v>
       </c>
       <c r="B70" t="str">
         <v>INFO</v>
       </c>
       <c r="C70" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.27s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.34s</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-06-23 05:14:32</v>
+        <v>2026-06-23 05:25:54</v>
       </c>
       <c r="B71" t="str">
         <v>INFO</v>
       </c>
       <c r="C71" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.99s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.45s</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-06-23 05:14:33</v>
+        <v>2026-06-23 05:25:55</v>
       </c>
       <c r="B72" t="str">
         <v>INFO</v>
       </c>
       <c r="C72" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.14s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.34s</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-06-23 05:14:34</v>
+        <v>2026-06-23 05:25:56</v>
       </c>
       <c r="B73" t="str">
         <v>INFO</v>
       </c>
       <c r="C73" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.26s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.47s</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026-06-23 05:14:35</v>
+        <v>2026-06-23 05:25:57</v>
       </c>
       <c r="B74" t="str">
         <v>INFO</v>
       </c>
       <c r="C74" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.87s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.23s</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026-06-23 05:14:36</v>
+        <v>2026-06-23 05:25:58</v>
       </c>
       <c r="B75" t="str">
         <v>INFO</v>
       </c>
       <c r="C75" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.50s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.58s</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026-06-23 05:14:37</v>
+        <v>2026-06-23 05:25:59</v>
       </c>
       <c r="B76" t="str">
         <v>INFO</v>
       </c>
       <c r="C76" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.01s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.53s</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026-06-23 05:14:38</v>
+        <v>2026-06-23 05:26:00</v>
       </c>
       <c r="B77" t="str">
         <v>INFO</v>
       </c>
       <c r="C77" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.58s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.77s</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026-06-23 05:14:39</v>
+        <v>2026-06-23 05:26:01</v>
       </c>
       <c r="B78" t="str">
         <v>INFO</v>
       </c>
       <c r="C78" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.76s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.21s</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026-06-23 05:14:40</v>
+        <v>2026-06-23 05:26:02</v>
       </c>
       <c r="B79" t="str">
         <v>INFO</v>
       </c>
       <c r="C79" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.41s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.05s</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026-06-23 05:14:41</v>
+        <v>2026-06-23 05:26:03</v>
       </c>
       <c r="B80" t="str">
         <v>INFO</v>
       </c>
       <c r="C80" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.92s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.33s</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026-06-23 05:14:42</v>
+        <v>2026-06-23 05:26:04</v>
       </c>
       <c r="B81" t="str">
         <v>INFO</v>
       </c>
       <c r="C81" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.88s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.21s</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026-06-23 05:14:43</v>
+        <v>2026-06-23 05:26:05</v>
       </c>
       <c r="B82" t="str">
         <v>INFO</v>
       </c>
       <c r="C82" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.39s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.50s</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026-06-23 05:14:44</v>
+        <v>2026-06-23 05:26:06</v>
       </c>
       <c r="B83" t="str">
         <v>INFO</v>
       </c>
       <c r="C83" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.30s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.52s</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026-06-23 05:14:45</v>
+        <v>2026-06-23 05:26:07</v>
       </c>
       <c r="B84" t="str">
         <v>INFO</v>
       </c>
       <c r="C84" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.06s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.77s</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2026-06-23 05:14:46</v>
+        <v>2026-06-23 05:26:08</v>
       </c>
       <c r="B85" t="str">
         <v>INFO</v>
       </c>
       <c r="C85" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.98s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.44s</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2026-06-23 05:14:47</v>
+        <v>2026-06-23 05:26:09</v>
       </c>
       <c r="B86" t="str">
         <v>INFO</v>
       </c>
       <c r="C86" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.29s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.88s</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2026-06-23 05:14:48</v>
+        <v>2026-06-23 05:26:10</v>
       </c>
       <c r="B87" t="str">
         <v>INFO</v>
       </c>
       <c r="C87" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.92s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.59s</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2026-06-23 05:14:49</v>
+        <v>2026-06-23 05:26:11</v>
       </c>
       <c r="B88" t="str">
         <v>INFO</v>
       </c>
       <c r="C88" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.35s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.69s</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2026-06-23 05:14:50</v>
+        <v>2026-06-23 05:26:12</v>
       </c>
       <c r="B89" t="str">
         <v>INFO</v>
       </c>
       <c r="C89" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.74s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.66s</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2026-06-23 05:14:51</v>
+        <v>2026-06-23 05:26:13</v>
       </c>
       <c r="B90" t="str">
         <v>INFO</v>
       </c>
       <c r="C90" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.89s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.83s</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2026-06-23 05:14:52</v>
+        <v>2026-06-23 05:26:14</v>
       </c>
       <c r="B91" t="str">
         <v>INFO</v>
       </c>
       <c r="C91" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.33s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.44s</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2026-06-23 05:14:53</v>
+        <v>2026-06-23 05:26:15</v>
       </c>
       <c r="B92" t="str">
         <v>INFO</v>
       </c>
       <c r="C92" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.29s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.13s</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2026-06-23 05:14:54</v>
+        <v>2026-06-23 05:26:16</v>
       </c>
       <c r="B93" t="str">
         <v>INFO</v>
       </c>
       <c r="C93" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.81s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.69s</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2026-06-23 05:14:55</v>
+        <v>2026-06-23 05:26:17</v>
       </c>
       <c r="B94" t="str">
         <v>INFO</v>
       </c>
       <c r="C94" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.19s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.91s</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2026-06-23 05:14:56</v>
+        <v>2026-06-23 05:26:18</v>
       </c>
       <c r="B95" t="str">
         <v>INFO</v>
       </c>
       <c r="C95" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.43s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.36s</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2026-06-23 05:14:57</v>
+        <v>2026-06-23 05:26:19</v>
       </c>
       <c r="B96" t="str">
         <v>INFO</v>
       </c>
       <c r="C96" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.58s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.40s</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2026-06-23 05:14:58</v>
+        <v>2026-06-23 05:26:20</v>
       </c>
       <c r="B97" t="str">
         <v>INFO</v>
       </c>
       <c r="C97" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.29s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.51s</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2026-06-23 05:14:59</v>
+        <v>2026-06-23 05:26:21</v>
       </c>
       <c r="B98" t="str">
         <v>INFO</v>
       </c>
       <c r="C98" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.15s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.17s</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2026-06-23 05:15:00</v>
+        <v>2026-06-23 05:26:22</v>
       </c>
       <c r="B99" t="str">
         <v>INFO</v>
       </c>
       <c r="C99" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.81s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.74s</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2026-06-23 05:15:01</v>
+        <v>2026-06-23 05:26:23</v>
       </c>
       <c r="B100" t="str">
         <v>INFO</v>
       </c>
       <c r="C100" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.74s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.24s</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>2026-06-23 05:15:02</v>
+        <v>2026-06-23 05:26:24</v>
       </c>
       <c r="B101" t="str">
         <v>INFO</v>
       </c>
       <c r="C101" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.86s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.03s</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>2026-06-23 05:15:03</v>
+        <v>2026-06-23 05:26:25</v>
       </c>
       <c r="B102" t="str">
         <v>INFO</v>
       </c>
       <c r="C102" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.95s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.39s</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2026-06-23 05:15:04</v>
+        <v>2026-06-23 05:26:26</v>
       </c>
       <c r="B103" t="str">
         <v>INFO</v>
       </c>
       <c r="C103" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.81s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.47s</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2026-06-23 05:15:05</v>
+        <v>2026-06-23 05:26:27</v>
       </c>
       <c r="B104" t="str">
         <v>INFO</v>
@@ -8521,2086 +8521,2086 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2026-06-23 05:15:06</v>
+        <v>2026-06-23 05:26:28</v>
       </c>
       <c r="B105" t="str">
         <v>INFO</v>
       </c>
       <c r="C105" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.28s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.40s</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2026-06-23 05:15:07</v>
+        <v>2026-06-23 05:26:29</v>
       </c>
       <c r="B106" t="str">
         <v>INFO</v>
       </c>
       <c r="C106" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.94s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.61s</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2026-06-23 05:15:08</v>
+        <v>2026-06-23 05:26:30</v>
       </c>
       <c r="B107" t="str">
         <v>INFO</v>
       </c>
       <c r="C107" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.54s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.18s</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>2026-06-23 05:15:09</v>
+        <v>2026-06-23 05:26:31</v>
       </c>
       <c r="B108" t="str">
         <v>INFO</v>
       </c>
       <c r="C108" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.91s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.39s</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>2026-06-23 05:15:10</v>
+        <v>2026-06-23 05:26:32</v>
       </c>
       <c r="B109" t="str">
         <v>INFO</v>
       </c>
       <c r="C109" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.98s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.43s</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2026-06-23 05:15:11</v>
+        <v>2026-06-23 05:26:33</v>
       </c>
       <c r="B110" t="str">
         <v>INFO</v>
       </c>
       <c r="C110" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.17s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.80s</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>2026-06-23 05:15:12</v>
+        <v>2026-06-23 05:26:34</v>
       </c>
       <c r="B111" t="str">
         <v>INFO</v>
       </c>
       <c r="C111" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.83s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.44s</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>2026-06-23 05:15:13</v>
+        <v>2026-06-23 05:26:35</v>
       </c>
       <c r="B112" t="str">
         <v>INFO</v>
       </c>
       <c r="C112" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.50s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.15s</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>2026-06-23 05:15:14</v>
+        <v>2026-06-23 05:26:36</v>
       </c>
       <c r="B113" t="str">
         <v>INFO</v>
       </c>
       <c r="C113" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.29s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.17s</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2026-06-23 05:15:15</v>
+        <v>2026-06-23 05:26:37</v>
       </c>
       <c r="B114" t="str">
         <v>INFO</v>
       </c>
       <c r="C114" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.90s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.83s</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2026-06-23 05:15:16</v>
+        <v>2026-06-23 05:26:38</v>
       </c>
       <c r="B115" t="str">
         <v>INFO</v>
       </c>
       <c r="C115" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.14s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.64s</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2026-06-23 05:15:17</v>
+        <v>2026-06-23 05:26:39</v>
       </c>
       <c r="B116" t="str">
         <v>INFO</v>
       </c>
       <c r="C116" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.31s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.14s</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2026-06-23 05:15:18</v>
+        <v>2026-06-23 05:26:40</v>
       </c>
       <c r="B117" t="str">
         <v>INFO</v>
       </c>
       <c r="C117" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.53s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.55s</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2026-06-23 05:15:19</v>
+        <v>2026-06-23 05:26:41</v>
       </c>
       <c r="B118" t="str">
         <v>INFO</v>
       </c>
       <c r="C118" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.27s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.04s</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2026-06-23 05:15:20</v>
+        <v>2026-06-23 05:26:42</v>
       </c>
       <c r="B119" t="str">
         <v>INFO</v>
       </c>
       <c r="C119" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.27s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.68s</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>2026-06-23 05:15:21</v>
+        <v>2026-06-23 05:26:43</v>
       </c>
       <c r="B120" t="str">
         <v>INFO</v>
       </c>
       <c r="C120" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.10s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.37s</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>2026-06-23 05:15:22</v>
+        <v>2026-06-23 05:26:44</v>
       </c>
       <c r="B121" t="str">
         <v>INFO</v>
       </c>
       <c r="C121" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.38s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.49s</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>2026-06-23 05:15:23</v>
+        <v>2026-06-23 05:26:45</v>
       </c>
       <c r="B122" t="str">
         <v>INFO</v>
       </c>
       <c r="C122" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.53s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.06s</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>2026-06-23 05:15:24</v>
+        <v>2026-06-23 05:26:46</v>
       </c>
       <c r="B123" t="str">
         <v>INFO</v>
       </c>
       <c r="C123" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.38s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.46s</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>2026-06-23 05:15:25</v>
+        <v>2026-06-23 05:26:47</v>
       </c>
       <c r="B124" t="str">
         <v>INFO</v>
       </c>
       <c r="C124" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.63s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.41s</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>2026-06-23 05:15:26</v>
+        <v>2026-06-23 05:26:48</v>
       </c>
       <c r="B125" t="str">
         <v>INFO</v>
       </c>
       <c r="C125" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.03s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.97s</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>2026-06-23 05:15:27</v>
+        <v>2026-06-23 05:26:49</v>
       </c>
       <c r="B126" t="str">
         <v>INFO</v>
       </c>
       <c r="C126" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.00s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.09s</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>2026-06-23 05:15:28</v>
+        <v>2026-06-23 05:26:50</v>
       </c>
       <c r="B127" t="str">
         <v>INFO</v>
       </c>
       <c r="C127" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.37s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.82s</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2026-06-23 05:15:29</v>
+        <v>2026-06-23 05:26:51</v>
       </c>
       <c r="B128" t="str">
         <v>INFO</v>
       </c>
       <c r="C128" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.96s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.13s</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>2026-06-23 05:15:30</v>
+        <v>2026-06-23 05:26:52</v>
       </c>
       <c r="B129" t="str">
         <v>INFO</v>
       </c>
       <c r="C129" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.29s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.62s</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>2026-06-23 05:15:31</v>
+        <v>2026-06-23 05:26:53</v>
       </c>
       <c r="B130" t="str">
         <v>INFO</v>
       </c>
       <c r="C130" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.86s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.79s</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>2026-06-23 05:15:32</v>
+        <v>2026-06-23 05:26:54</v>
       </c>
       <c r="B131" t="str">
         <v>INFO</v>
       </c>
       <c r="C131" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.34s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.55s</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>2026-06-23 05:15:33</v>
+        <v>2026-06-23 05:26:55</v>
       </c>
       <c r="B132" t="str">
         <v>INFO</v>
       </c>
       <c r="C132" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.17s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.91s</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>2026-06-23 05:15:34</v>
+        <v>2026-06-23 05:26:56</v>
       </c>
       <c r="B133" t="str">
         <v>INFO</v>
       </c>
       <c r="C133" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.27s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.49s</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>2026-06-23 05:15:35</v>
+        <v>2026-06-23 05:26:57</v>
       </c>
       <c r="B134" t="str">
         <v>INFO</v>
       </c>
       <c r="C134" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.43s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.37s</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>2026-06-23 05:15:36</v>
+        <v>2026-06-23 05:26:58</v>
       </c>
       <c r="B135" t="str">
         <v>INFO</v>
       </c>
       <c r="C135" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.15s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.41s</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>2026-06-23 05:15:37</v>
+        <v>2026-06-23 05:26:59</v>
       </c>
       <c r="B136" t="str">
         <v>INFO</v>
       </c>
       <c r="C136" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.26s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.03s</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2026-06-23 05:15:38</v>
+        <v>2026-06-23 05:27:00</v>
       </c>
       <c r="B137" t="str">
         <v>INFO</v>
       </c>
       <c r="C137" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.80s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.08s</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2026-06-23 05:15:39</v>
+        <v>2026-06-23 05:27:01</v>
       </c>
       <c r="B138" t="str">
         <v>INFO</v>
       </c>
       <c r="C138" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.45s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.65s</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>2026-06-23 05:15:40</v>
+        <v>2026-06-23 05:27:02</v>
       </c>
       <c r="B139" t="str">
         <v>INFO</v>
       </c>
       <c r="C139" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.06s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.25s</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2026-06-23 05:15:41</v>
+        <v>2026-06-23 05:27:03</v>
       </c>
       <c r="B140" t="str">
         <v>INFO</v>
       </c>
       <c r="C140" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.42s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.81s</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>2026-06-23 05:15:42</v>
+        <v>2026-06-23 05:27:04</v>
       </c>
       <c r="B141" t="str">
         <v>INFO</v>
       </c>
       <c r="C141" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.03s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.83s</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2026-06-23 05:15:43</v>
+        <v>2026-06-23 05:27:05</v>
       </c>
       <c r="B142" t="str">
         <v>INFO</v>
       </c>
       <c r="C142" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.97s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.16s</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>2026-06-23 05:15:44</v>
+        <v>2026-06-23 05:27:06</v>
       </c>
       <c r="B143" t="str">
         <v>INFO</v>
       </c>
       <c r="C143" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.22s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.65s</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>2026-06-23 05:15:45</v>
+        <v>2026-06-23 05:27:07</v>
       </c>
       <c r="B144" t="str">
         <v>INFO</v>
       </c>
       <c r="C144" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.54s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.11s</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>2026-06-23 05:15:46</v>
+        <v>2026-06-23 05:27:08</v>
       </c>
       <c r="B145" t="str">
         <v>INFO</v>
       </c>
       <c r="C145" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.11s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.96s</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>2026-06-23 05:15:47</v>
+        <v>2026-06-23 05:27:09</v>
       </c>
       <c r="B146" t="str">
         <v>INFO</v>
       </c>
       <c r="C146" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.99s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.10s</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>2026-06-23 05:15:48</v>
+        <v>2026-06-23 05:27:10</v>
       </c>
       <c r="B147" t="str">
         <v>INFO</v>
       </c>
       <c r="C147" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.46s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.85s</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>2026-06-23 05:15:49</v>
+        <v>2026-06-23 05:27:11</v>
       </c>
       <c r="B148" t="str">
         <v>INFO</v>
       </c>
       <c r="C148" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.43s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.17s</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>2026-06-23 05:15:50</v>
+        <v>2026-06-23 05:27:12</v>
       </c>
       <c r="B149" t="str">
         <v>INFO</v>
       </c>
       <c r="C149" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.15s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.35s</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>2026-06-23 05:15:51</v>
+        <v>2026-06-23 05:27:13</v>
       </c>
       <c r="B150" t="str">
         <v>INFO</v>
       </c>
       <c r="C150" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.13s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.43s</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>2026-06-23 05:15:52</v>
+        <v>2026-06-23 05:27:14</v>
       </c>
       <c r="B151" t="str">
         <v>INFO</v>
       </c>
       <c r="C151" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.65s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.34s</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>2026-06-23 05:15:53</v>
+        <v>2026-06-23 05:27:15</v>
       </c>
       <c r="B152" t="str">
         <v>INFO</v>
       </c>
       <c r="C152" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.05s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.67s</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>2026-06-23 05:15:54</v>
+        <v>2026-06-23 05:27:16</v>
       </c>
       <c r="B153" t="str">
         <v>INFO</v>
       </c>
       <c r="C153" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.23s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.66s</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>2026-06-23 05:15:55</v>
+        <v>2026-06-23 05:27:17</v>
       </c>
       <c r="B154" t="str">
         <v>INFO</v>
       </c>
       <c r="C154" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.85s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.67s</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>2026-06-23 05:15:56</v>
+        <v>2026-06-23 05:27:18</v>
       </c>
       <c r="B155" t="str">
         <v>INFO</v>
       </c>
       <c r="C155" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.83s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.74s</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>2026-06-23 05:15:57</v>
+        <v>2026-06-23 05:27:19</v>
       </c>
       <c r="B156" t="str">
         <v>INFO</v>
       </c>
       <c r="C156" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.92s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.40s</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>2026-06-23 05:15:58</v>
+        <v>2026-06-23 05:27:20</v>
       </c>
       <c r="B157" t="str">
         <v>INFO</v>
       </c>
       <c r="C157" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.28s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.64s</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>2026-06-23 05:15:59</v>
+        <v>2026-06-23 05:27:21</v>
       </c>
       <c r="B158" t="str">
         <v>INFO</v>
       </c>
       <c r="C158" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.00s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.17s</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>2026-06-23 05:16:00</v>
+        <v>2026-06-23 05:27:22</v>
       </c>
       <c r="B159" t="str">
         <v>INFO</v>
       </c>
       <c r="C159" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.34s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.88s</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>2026-06-23 05:16:01</v>
+        <v>2026-06-23 05:27:23</v>
       </c>
       <c r="B160" t="str">
         <v>INFO</v>
       </c>
       <c r="C160" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.76s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.69s</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>2026-06-23 05:16:02</v>
+        <v>2026-06-23 05:27:24</v>
       </c>
       <c r="B161" t="str">
         <v>INFO</v>
       </c>
       <c r="C161" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.36s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.90s</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>2026-06-23 05:16:03</v>
+        <v>2026-06-23 05:27:25</v>
       </c>
       <c r="B162" t="str">
         <v>INFO</v>
       </c>
       <c r="C162" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.23s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.92s</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>2026-06-23 05:16:04</v>
+        <v>2026-06-23 05:27:26</v>
       </c>
       <c r="B163" t="str">
         <v>INFO</v>
       </c>
       <c r="C163" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.94s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.81s</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>2026-06-23 05:16:05</v>
+        <v>2026-06-23 05:27:27</v>
       </c>
       <c r="B164" t="str">
         <v>INFO</v>
       </c>
       <c r="C164" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.42s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.46s</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>2026-06-23 05:16:06</v>
+        <v>2026-06-23 05:27:28</v>
       </c>
       <c r="B165" t="str">
         <v>INFO</v>
       </c>
       <c r="C165" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.97s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.70s</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>2026-06-23 05:16:07</v>
+        <v>2026-06-23 05:27:29</v>
       </c>
       <c r="B166" t="str">
         <v>INFO</v>
       </c>
       <c r="C166" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.13s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.56s</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>2026-06-23 05:16:08</v>
+        <v>2026-06-23 05:27:30</v>
       </c>
       <c r="B167" t="str">
         <v>INFO</v>
       </c>
       <c r="C167" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.41s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.01s</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>2026-06-23 05:16:09</v>
+        <v>2026-06-23 05:27:31</v>
       </c>
       <c r="B168" t="str">
         <v>INFO</v>
       </c>
       <c r="C168" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.31s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.84s</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>2026-06-23 05:16:10</v>
+        <v>2026-06-23 05:27:32</v>
       </c>
       <c r="B169" t="str">
         <v>INFO</v>
       </c>
       <c r="C169" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.81s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.90s</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>2026-06-23 05:16:11</v>
+        <v>2026-06-23 05:27:33</v>
       </c>
       <c r="B170" t="str">
         <v>INFO</v>
       </c>
       <c r="C170" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.01s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.32s</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>2026-06-23 05:16:12</v>
+        <v>2026-06-23 05:27:34</v>
       </c>
       <c r="B171" t="str">
         <v>INFO</v>
       </c>
       <c r="C171" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.98s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.13s</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>2026-06-23 05:16:13</v>
+        <v>2026-06-23 05:27:35</v>
       </c>
       <c r="B172" t="str">
         <v>INFO</v>
       </c>
       <c r="C172" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.41s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.62s</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>2026-06-23 05:16:14</v>
+        <v>2026-06-23 05:27:36</v>
       </c>
       <c r="B173" t="str">
         <v>INFO</v>
       </c>
       <c r="C173" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.24s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.38s</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>2026-06-23 05:16:15</v>
+        <v>2026-06-23 05:27:37</v>
       </c>
       <c r="B174" t="str">
         <v>INFO</v>
       </c>
       <c r="C174" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.11s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.85s</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>2026-06-23 05:16:16</v>
+        <v>2026-06-23 05:27:38</v>
       </c>
       <c r="B175" t="str">
         <v>INFO</v>
       </c>
       <c r="C175" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.12s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.92s</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>2026-06-23 05:16:17</v>
+        <v>2026-06-23 05:27:39</v>
       </c>
       <c r="B176" t="str">
         <v>INFO</v>
       </c>
       <c r="C176" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.00s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.70s</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>2026-06-23 05:16:18</v>
+        <v>2026-06-23 05:27:40</v>
       </c>
       <c r="B177" t="str">
         <v>INFO</v>
       </c>
       <c r="C177" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.95s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.97s</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>2026-06-23 05:16:19</v>
+        <v>2026-06-23 05:27:41</v>
       </c>
       <c r="B178" t="str">
         <v>INFO</v>
       </c>
       <c r="C178" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.08s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.09s</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>2026-06-23 05:16:20</v>
+        <v>2026-06-23 05:27:42</v>
       </c>
       <c r="B179" t="str">
         <v>INFO</v>
       </c>
       <c r="C179" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.70s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.64s</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>2026-06-23 05:16:21</v>
+        <v>2026-06-23 05:27:43</v>
       </c>
       <c r="B180" t="str">
         <v>INFO</v>
       </c>
       <c r="C180" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.94s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.21s</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>2026-06-23 05:16:22</v>
+        <v>2026-06-23 05:27:44</v>
       </c>
       <c r="B181" t="str">
         <v>INFO</v>
       </c>
       <c r="C181" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.30s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.44s</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>2026-06-23 05:16:23</v>
+        <v>2026-06-23 05:27:45</v>
       </c>
       <c r="B182" t="str">
         <v>INFO</v>
       </c>
       <c r="C182" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.38s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.71s</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>2026-06-23 05:16:24</v>
+        <v>2026-06-23 05:27:46</v>
       </c>
       <c r="B183" t="str">
         <v>INFO</v>
       </c>
       <c r="C183" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.99s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.47s</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>2026-06-23 05:16:25</v>
+        <v>2026-06-23 05:27:47</v>
       </c>
       <c r="B184" t="str">
         <v>INFO</v>
       </c>
       <c r="C184" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.63s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.33s</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>2026-06-23 05:16:26</v>
+        <v>2026-06-23 05:27:48</v>
       </c>
       <c r="B185" t="str">
         <v>INFO</v>
       </c>
       <c r="C185" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.27s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.39s</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>2026-06-23 05:16:27</v>
+        <v>2026-06-23 05:27:49</v>
       </c>
       <c r="B186" t="str">
         <v>INFO</v>
       </c>
       <c r="C186" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.37s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.47s</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>2026-06-23 05:16:28</v>
+        <v>2026-06-23 05:27:50</v>
       </c>
       <c r="B187" t="str">
         <v>INFO</v>
       </c>
       <c r="C187" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.01s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.11s</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>2026-06-23 05:16:29</v>
+        <v>2026-06-23 05:27:51</v>
       </c>
       <c r="B188" t="str">
         <v>INFO</v>
       </c>
       <c r="C188" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.36s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.37s</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>2026-06-23 05:16:30</v>
+        <v>2026-06-23 05:27:52</v>
       </c>
       <c r="B189" t="str">
         <v>INFO</v>
       </c>
       <c r="C189" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.06s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.52s</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>2026-06-23 05:16:31</v>
+        <v>2026-06-23 05:27:53</v>
       </c>
       <c r="B190" t="str">
         <v>INFO</v>
       </c>
       <c r="C190" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.64s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.45s</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>2026-06-23 05:16:32</v>
+        <v>2026-06-23 05:27:54</v>
       </c>
       <c r="B191" t="str">
         <v>INFO</v>
       </c>
       <c r="C191" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.97s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.33s</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>2026-06-23 05:16:33</v>
+        <v>2026-06-23 05:27:55</v>
       </c>
       <c r="B192" t="str">
         <v>INFO</v>
       </c>
       <c r="C192" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.23s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.19s</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>2026-06-23 05:16:34</v>
+        <v>2026-06-23 05:27:56</v>
       </c>
       <c r="B193" t="str">
         <v>INFO</v>
       </c>
       <c r="C193" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.09s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.16s</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>2026-06-23 05:16:35</v>
+        <v>2026-06-23 05:27:57</v>
       </c>
       <c r="B194" t="str">
         <v>INFO</v>
       </c>
       <c r="C194" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.25s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.46s</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>2026-06-23 05:16:36</v>
+        <v>2026-06-23 05:27:58</v>
       </c>
       <c r="B195" t="str">
         <v>INFO</v>
       </c>
       <c r="C195" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.49s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.23s</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>2026-06-23 05:16:37</v>
+        <v>2026-06-23 05:27:59</v>
       </c>
       <c r="B196" t="str">
         <v>INFO</v>
       </c>
       <c r="C196" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.28s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.12s</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>2026-06-23 05:16:38</v>
+        <v>2026-06-23 05:28:00</v>
       </c>
       <c r="B197" t="str">
         <v>INFO</v>
       </c>
       <c r="C197" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.15s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.23s</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>2026-06-23 05:16:39</v>
+        <v>2026-06-23 05:28:01</v>
       </c>
       <c r="B198" t="str">
         <v>INFO</v>
       </c>
       <c r="C198" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.79s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.62s</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>2026-06-23 05:16:40</v>
+        <v>2026-06-23 05:28:02</v>
       </c>
       <c r="B199" t="str">
         <v>INFO</v>
       </c>
       <c r="C199" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.56s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.22s</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>2026-06-23 05:16:41</v>
+        <v>2026-06-23 05:28:03</v>
       </c>
       <c r="B200" t="str">
         <v>INFO</v>
       </c>
       <c r="C200" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.33s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.83s</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>2026-06-23 05:16:42</v>
+        <v>2026-06-23 05:28:04</v>
       </c>
       <c r="B201" t="str">
         <v>INFO</v>
       </c>
       <c r="C201" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.89s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.21s</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>2026-06-23 05:16:43</v>
+        <v>2026-06-23 05:28:05</v>
       </c>
       <c r="B202" t="str">
         <v>INFO</v>
       </c>
       <c r="C202" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.12s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.87s</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>2026-06-23 05:16:44</v>
+        <v>2026-06-23 05:28:06</v>
       </c>
       <c r="B203" t="str">
         <v>INFO</v>
       </c>
       <c r="C203" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.97s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.34s</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>2026-06-23 05:16:45</v>
+        <v>2026-06-23 05:28:07</v>
       </c>
       <c r="B204" t="str">
         <v>INFO</v>
       </c>
       <c r="C204" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.87s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.62s</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>2026-06-23 05:16:46</v>
+        <v>2026-06-23 05:28:08</v>
       </c>
       <c r="B205" t="str">
         <v>INFO</v>
       </c>
       <c r="C205" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.45s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.06s</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>2026-06-23 05:16:47</v>
+        <v>2026-06-23 05:28:09</v>
       </c>
       <c r="B206" t="str">
         <v>INFO</v>
       </c>
       <c r="C206" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.70s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.32s</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>2026-06-23 05:16:48</v>
+        <v>2026-06-23 05:28:10</v>
       </c>
       <c r="B207" t="str">
         <v>INFO</v>
       </c>
       <c r="C207" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.88s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.39s</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>2026-06-23 05:16:49</v>
+        <v>2026-06-23 05:28:11</v>
       </c>
       <c r="B208" t="str">
         <v>INFO</v>
       </c>
       <c r="C208" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.12s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.10s</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>2026-06-23 05:16:50</v>
+        <v>2026-06-23 05:28:12</v>
       </c>
       <c r="B209" t="str">
         <v>INFO</v>
       </c>
       <c r="C209" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.62s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.34s</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>2026-06-23 05:16:51</v>
+        <v>2026-06-23 05:28:13</v>
       </c>
       <c r="B210" t="str">
         <v>INFO</v>
       </c>
       <c r="C210" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.78s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.32s</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>2026-06-23 05:16:52</v>
+        <v>2026-06-23 05:28:14</v>
       </c>
       <c r="B211" t="str">
         <v>INFO</v>
       </c>
       <c r="C211" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.76s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.26s</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>2026-06-23 05:16:53</v>
+        <v>2026-06-23 05:28:15</v>
       </c>
       <c r="B212" t="str">
         <v>INFO</v>
       </c>
       <c r="C212" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.68s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.55s</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>2026-06-23 05:16:54</v>
+        <v>2026-06-23 05:28:16</v>
       </c>
       <c r="B213" t="str">
         <v>INFO</v>
       </c>
       <c r="C213" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.33s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.42s</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>2026-06-23 05:16:55</v>
+        <v>2026-06-23 05:28:17</v>
       </c>
       <c r="B214" t="str">
         <v>INFO</v>
       </c>
       <c r="C214" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.64s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.81s</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>2026-06-23 05:16:56</v>
+        <v>2026-06-23 05:28:18</v>
       </c>
       <c r="B215" t="str">
         <v>INFO</v>
       </c>
       <c r="C215" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.08s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.38s</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>2026-06-23 05:16:57</v>
+        <v>2026-06-23 05:28:19</v>
       </c>
       <c r="B216" t="str">
         <v>INFO</v>
       </c>
       <c r="C216" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.81s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.51s</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>2026-06-23 05:16:58</v>
+        <v>2026-06-23 05:28:20</v>
       </c>
       <c r="B217" t="str">
         <v>INFO</v>
       </c>
       <c r="C217" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.70s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.75s</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>2026-06-23 05:16:59</v>
+        <v>2026-06-23 05:28:21</v>
       </c>
       <c r="B218" t="str">
         <v>INFO</v>
       </c>
       <c r="C218" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.91s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.53s</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>2026-06-23 05:17:00</v>
+        <v>2026-06-23 05:28:22</v>
       </c>
       <c r="B219" t="str">
         <v>INFO</v>
       </c>
       <c r="C219" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.02s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.70s</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>2026-06-23 05:17:01</v>
+        <v>2026-06-23 05:28:23</v>
       </c>
       <c r="B220" t="str">
         <v>INFO</v>
       </c>
       <c r="C220" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.12s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.54s</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>2026-06-23 05:17:02</v>
+        <v>2026-06-23 05:28:24</v>
       </c>
       <c r="B221" t="str">
         <v>INFO</v>
       </c>
       <c r="C221" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.97s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.65s</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>2026-06-23 05:17:03</v>
+        <v>2026-06-23 05:28:25</v>
       </c>
       <c r="B222" t="str">
         <v>INFO</v>
       </c>
       <c r="C222" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.19s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.15s</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>2026-06-23 05:17:04</v>
+        <v>2026-06-23 05:28:26</v>
       </c>
       <c r="B223" t="str">
         <v>INFO</v>
       </c>
       <c r="C223" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.39s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.17s</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>2026-06-23 05:17:05</v>
+        <v>2026-06-23 05:28:27</v>
       </c>
       <c r="B224" t="str">
         <v>INFO</v>
       </c>
       <c r="C224" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.78s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.08s</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>2026-06-23 05:17:06</v>
+        <v>2026-06-23 05:28:28</v>
       </c>
       <c r="B225" t="str">
         <v>INFO</v>
       </c>
       <c r="C225" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.89s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.45s</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>2026-06-23 05:17:07</v>
+        <v>2026-06-23 05:28:29</v>
       </c>
       <c r="B226" t="str">
         <v>INFO</v>
       </c>
       <c r="C226" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.09s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.15s</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>2026-06-23 05:17:08</v>
+        <v>2026-06-23 05:28:30</v>
       </c>
       <c r="B227" t="str">
         <v>INFO</v>
       </c>
       <c r="C227" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.24s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.14s</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>2026-06-23 05:17:09</v>
+        <v>2026-06-23 05:28:31</v>
       </c>
       <c r="B228" t="str">
         <v>INFO</v>
       </c>
       <c r="C228" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.68s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.73s</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>2026-06-23 05:17:10</v>
+        <v>2026-06-23 05:28:32</v>
       </c>
       <c r="B229" t="str">
         <v>INFO</v>
       </c>
       <c r="C229" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.92s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.40s</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>2026-06-23 05:17:11</v>
+        <v>2026-06-23 05:28:33</v>
       </c>
       <c r="B230" t="str">
         <v>INFO</v>
       </c>
       <c r="C230" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.99s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.80s</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>2026-06-23 05:17:12</v>
+        <v>2026-06-23 05:28:34</v>
       </c>
       <c r="B231" t="str">
         <v>INFO</v>
       </c>
       <c r="C231" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.21s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.18s</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>2026-06-23 05:17:13</v>
+        <v>2026-06-23 05:28:35</v>
       </c>
       <c r="B232" t="str">
         <v>INFO</v>
       </c>
       <c r="C232" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.07s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.92s</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>2026-06-23 05:17:14</v>
+        <v>2026-06-23 05:28:36</v>
       </c>
       <c r="B233" t="str">
         <v>INFO</v>
       </c>
       <c r="C233" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.09s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.00s</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>2026-06-23 05:17:15</v>
+        <v>2026-06-23 05:28:37</v>
       </c>
       <c r="B234" t="str">
         <v>INFO</v>
       </c>
       <c r="C234" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.31s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.67s</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>2026-06-23 05:17:16</v>
+        <v>2026-06-23 05:28:38</v>
       </c>
       <c r="B235" t="str">
         <v>INFO</v>
       </c>
       <c r="C235" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.14s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.16s</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>2026-06-23 05:17:17</v>
+        <v>2026-06-23 05:28:39</v>
       </c>
       <c r="B236" t="str">
         <v>INFO</v>
       </c>
       <c r="C236" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.17s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.82s</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>2026-06-23 05:17:18</v>
+        <v>2026-06-23 05:28:40</v>
       </c>
       <c r="B237" t="str">
         <v>INFO</v>
       </c>
       <c r="C237" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.81s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.27s</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>2026-06-23 05:17:19</v>
+        <v>2026-06-23 05:28:41</v>
       </c>
       <c r="B238" t="str">
         <v>INFO</v>
       </c>
       <c r="C238" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.32s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.18s</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>2026-06-23 05:17:20</v>
+        <v>2026-06-23 05:28:42</v>
       </c>
       <c r="B239" t="str">
         <v>INFO</v>
       </c>
       <c r="C239" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.30s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.32s</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>2026-06-23 05:17:21</v>
+        <v>2026-06-23 05:28:43</v>
       </c>
       <c r="B240" t="str">
         <v>INFO</v>
       </c>
       <c r="C240" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.96s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.02s</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>2026-06-23 05:17:22</v>
+        <v>2026-06-23 05:28:44</v>
       </c>
       <c r="B241" t="str">
         <v>INFO</v>
       </c>
       <c r="C241" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.13s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.30s</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>2026-06-23 05:17:23</v>
+        <v>2026-06-23 05:28:45</v>
       </c>
       <c r="B242" t="str">
         <v>INFO</v>
       </c>
       <c r="C242" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.89s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.44s</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>2026-06-23 05:17:24</v>
+        <v>2026-06-23 05:28:46</v>
       </c>
       <c r="B243" t="str">
         <v>INFO</v>
       </c>
       <c r="C243" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.74s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.10s</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>2026-06-23 05:17:25</v>
+        <v>2026-06-23 05:28:47</v>
       </c>
       <c r="B244" t="str">
         <v>INFO</v>
       </c>
       <c r="C244" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.31s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.34s</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>2026-06-23 05:17:26</v>
+        <v>2026-06-23 05:28:48</v>
       </c>
       <c r="B245" t="str">
         <v>INFO</v>
       </c>
       <c r="C245" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.29s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.92s</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>2026-06-23 05:17:27</v>
+        <v>2026-06-23 05:28:49</v>
       </c>
       <c r="B246" t="str">
         <v>INFO</v>
       </c>
       <c r="C246" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.22s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.99s</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>2026-06-23 05:17:28</v>
+        <v>2026-06-23 05:28:50</v>
       </c>
       <c r="B247" t="str">
         <v>INFO</v>
       </c>
       <c r="C247" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.80s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.97s</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>2026-06-23 05:17:29</v>
+        <v>2026-06-23 05:28:51</v>
       </c>
       <c r="B248" t="str">
         <v>INFO</v>
       </c>
       <c r="C248" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.23s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.91s</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>2026-06-23 05:17:30</v>
+        <v>2026-06-23 05:28:52</v>
       </c>
       <c r="B249" t="str">
         <v>INFO</v>
       </c>
       <c r="C249" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.26s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.44s</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>2026-06-23 05:17:31</v>
+        <v>2026-06-23 05:28:53</v>
       </c>
       <c r="B250" t="str">
         <v>INFO</v>
       </c>
       <c r="C250" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.56s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.10s</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>2026-06-23 05:17:32</v>
+        <v>2026-06-23 05:28:54</v>
       </c>
       <c r="B251" t="str">
         <v>INFO</v>
       </c>
       <c r="C251" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.85s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.19s</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>2026-06-23 05:17:33</v>
+        <v>2026-06-23 05:28:55</v>
       </c>
       <c r="B252" t="str">
         <v>INFO</v>
       </c>
       <c r="C252" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.08s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.28s</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>2026-06-23 05:17:34</v>
+        <v>2026-06-23 05:28:56</v>
       </c>
       <c r="B253" t="str">
         <v>INFO</v>
       </c>
       <c r="C253" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.81s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.03s</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>2026-06-23 05:17:35</v>
+        <v>2026-06-23 05:28:57</v>
       </c>
       <c r="B254" t="str">
         <v>INFO</v>
       </c>
       <c r="C254" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.85s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.33s</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>2026-06-23 05:17:36</v>
+        <v>2026-06-23 05:28:58</v>
       </c>
       <c r="B255" t="str">
         <v>INFO</v>
       </c>
       <c r="C255" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.29s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.43s</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>2026-06-23 05:17:37</v>
+        <v>2026-06-23 05:28:59</v>
       </c>
       <c r="B256" t="str">
         <v>INFO</v>
       </c>
       <c r="C256" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.61s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.12s</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>2026-06-23 05:17:38</v>
+        <v>2026-06-23 05:29:00</v>
       </c>
       <c r="B257" t="str">
         <v>INFO</v>
       </c>
       <c r="C257" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.54s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.12s</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>2026-06-23 05:17:39</v>
+        <v>2026-06-23 05:29:01</v>
       </c>
       <c r="B258" t="str">
         <v>INFO</v>
       </c>
       <c r="C258" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.65s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.28s</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>2026-06-23 05:17:40</v>
+        <v>2026-06-23 05:29:02</v>
       </c>
       <c r="B259" t="str">
         <v>INFO</v>
       </c>
       <c r="C259" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.16s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.82s</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>2026-06-23 05:17:41</v>
+        <v>2026-06-23 05:29:03</v>
       </c>
       <c r="B260" t="str">
         <v>INFO</v>
       </c>
       <c r="C260" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.01s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.50s</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>2026-06-23 05:17:42</v>
+        <v>2026-06-23 05:29:04</v>
       </c>
       <c r="B261" t="str">
         <v>INFO</v>
       </c>
       <c r="C261" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.28s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.21s</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>2026-06-23 05:17:43</v>
+        <v>2026-06-23 05:29:05</v>
       </c>
       <c r="B262" t="str">
         <v>INFO</v>
       </c>
       <c r="C262" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.07s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.25s</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>2026-06-23 05:17:44</v>
+        <v>2026-06-23 05:29:06</v>
       </c>
       <c r="B263" t="str">
         <v>INFO</v>
       </c>
       <c r="C263" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.91s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.90s</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>2026-06-23 05:17:45</v>
+        <v>2026-06-23 05:29:07</v>
       </c>
       <c r="B264" t="str">
         <v>INFO</v>
       </c>
       <c r="C264" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.32s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.04s</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>2026-06-23 05:17:46</v>
+        <v>2026-06-23 05:29:08</v>
       </c>
       <c r="B265" t="str">
         <v>INFO</v>
       </c>
       <c r="C265" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.52s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.49s</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>2026-06-23 05:17:47</v>
+        <v>2026-06-23 05:29:09</v>
       </c>
       <c r="B266" t="str">
         <v>INFO</v>
       </c>
       <c r="C266" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.87s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.74s</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>2026-06-23 05:17:48</v>
+        <v>2026-06-23 05:29:10</v>
       </c>
       <c r="B267" t="str">
         <v>INFO</v>
       </c>
       <c r="C267" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.10s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.07s</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>2026-06-23 05:17:49</v>
+        <v>2026-06-23 05:29:11</v>
       </c>
       <c r="B268" t="str">
         <v>INFO</v>
       </c>
       <c r="C268" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.30s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.00s</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>2026-06-23 05:17:50</v>
+        <v>2026-06-23 05:29:12</v>
       </c>
       <c r="B269" t="str">
         <v>INFO</v>
       </c>
       <c r="C269" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.79s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.31s</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>2026-06-23 05:17:51</v>
+        <v>2026-06-23 05:29:13</v>
       </c>
       <c r="B270" t="str">
         <v>INFO</v>
       </c>
       <c r="C270" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.11s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.23s</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>2026-06-23 05:17:52</v>
+        <v>2026-06-23 05:29:14</v>
       </c>
       <c r="B271" t="str">
         <v>INFO</v>
       </c>
       <c r="C271" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.37s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.28s</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>2026-06-23 05:17:53</v>
+        <v>2026-06-23 05:29:15</v>
       </c>
       <c r="B272" t="str">
         <v>INFO</v>
       </c>
       <c r="C272" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.37s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.11s</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>2026-06-23 05:17:54</v>
+        <v>2026-06-23 05:29:16</v>
       </c>
       <c r="B273" t="str">
         <v>INFO</v>
       </c>
       <c r="C273" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.14s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.77s</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>2026-06-23 05:17:55</v>
+        <v>2026-06-23 05:29:17</v>
       </c>
       <c r="B274" t="str">
         <v>INFO</v>
       </c>
       <c r="C274" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.04s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.76s</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>2026-06-23 05:17:56</v>
+        <v>2026-06-23 05:29:18</v>
       </c>
       <c r="B275" t="str">
         <v>INFO</v>
       </c>
       <c r="C275" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.43s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.39s</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>2026-06-23 05:17:57</v>
+        <v>2026-06-23 05:29:19</v>
       </c>
       <c r="B276" t="str">
         <v>INFO</v>
       </c>
       <c r="C276" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.09s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.44s</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>2026-06-23 05:17:58</v>
+        <v>2026-06-23 05:29:20</v>
       </c>
       <c r="B277" t="str">
         <v>INFO</v>
       </c>
       <c r="C277" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.38s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.46s</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>2026-06-23 05:17:59</v>
+        <v>2026-06-23 05:29:21</v>
       </c>
       <c r="B278" t="str">
         <v>INFO</v>
       </c>
       <c r="C278" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.51s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.30s</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>2026-06-23 05:18:00</v>
+        <v>2026-06-23 05:29:22</v>
       </c>
       <c r="B279" t="str">
         <v>INFO</v>
       </c>
       <c r="C279" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.56s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.73s</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>2026-06-23 05:18:01</v>
+        <v>2026-06-23 05:29:23</v>
       </c>
       <c r="B280" t="str">
         <v>INFO</v>
       </c>
       <c r="C280" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.28s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.73s</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>2026-06-23 05:18:02</v>
+        <v>2026-06-23 05:29:24</v>
       </c>
       <c r="B281" t="str">
         <v>INFO</v>
       </c>
       <c r="C281" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.80s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.25s</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>2026-06-23 05:18:03</v>
+        <v>2026-06-23 05:29:25</v>
       </c>
       <c r="B282" t="str">
         <v>INFO</v>
       </c>
       <c r="C282" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.72s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.38s</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>2026-06-23 05:18:04</v>
+        <v>2026-06-23 05:29:26</v>
       </c>
       <c r="B283" t="str">
         <v>INFO</v>
       </c>
       <c r="C283" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.19s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.19s</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>2026-06-23 05:18:05</v>
+        <v>2026-06-23 05:29:27</v>
       </c>
       <c r="B284" t="str">
         <v>INFO</v>
       </c>
       <c r="C284" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.86s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.51s</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>2026-06-23 05:18:06</v>
+        <v>2026-06-23 05:29:28</v>
       </c>
       <c r="B285" t="str">
         <v>INFO</v>
       </c>
       <c r="C285" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.69s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.89s</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>2026-06-23 05:18:07</v>
+        <v>2026-06-23 05:29:29</v>
       </c>
       <c r="B286" t="str">
         <v>INFO</v>
       </c>
       <c r="C286" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.90s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.79s</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>2026-06-23 05:18:08</v>
+        <v>2026-06-23 05:29:30</v>
       </c>
       <c r="B287" t="str">
         <v>INFO</v>
       </c>
       <c r="C287" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.35s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.34s</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>2026-06-23 05:18:09</v>
+        <v>2026-06-23 05:29:31</v>
       </c>
       <c r="B288" t="str">
         <v>INFO</v>
       </c>
       <c r="C288" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.57s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.35s</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>2026-06-23 05:18:10</v>
+        <v>2026-06-23 05:29:32</v>
       </c>
       <c r="B289" t="str">
         <v>INFO</v>
       </c>
       <c r="C289" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.95s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.41s</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>2026-06-23 05:18:11</v>
+        <v>2026-06-23 05:29:33</v>
       </c>
       <c r="B290" t="str">
         <v>INFO</v>
       </c>
       <c r="C290" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.46s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.09s</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>2026-06-23 05:18:12</v>
+        <v>2026-06-23 05:29:34</v>
       </c>
       <c r="B291" t="str">
         <v>INFO</v>
       </c>
       <c r="C291" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.61s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.41s</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>2026-06-23 05:18:13</v>
+        <v>2026-06-23 05:29:35</v>
       </c>
       <c r="B292" t="str">
         <v>INFO</v>
       </c>
       <c r="C292" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.84s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.65s</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>2026-06-23 05:18:14</v>
+        <v>2026-06-23 05:29:36</v>
       </c>
       <c r="B293" t="str">
         <v>INFO</v>
       </c>
       <c r="C293" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.77s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.48s</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>2026-06-23 05:18:15</v>
+        <v>2026-06-23 05:29:37</v>
       </c>
       <c r="B294" t="str">
         <v>INFO</v>
@@ -10611,315 +10611,315 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>2026-06-23 05:18:16</v>
+        <v>2026-06-23 05:29:38</v>
       </c>
       <c r="B295" t="str">
         <v>INFO</v>
       </c>
       <c r="C295" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.18s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.76s</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>2026-06-23 05:18:17</v>
+        <v>2026-06-23 05:29:39</v>
       </c>
       <c r="B296" t="str">
         <v>INFO</v>
       </c>
       <c r="C296" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.22s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.17s</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>2026-06-23 05:18:18</v>
+        <v>2026-06-23 05:29:40</v>
       </c>
       <c r="B297" t="str">
         <v>INFO</v>
       </c>
       <c r="C297" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.72s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.04s</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>2026-06-23 05:18:19</v>
+        <v>2026-06-23 05:29:41</v>
       </c>
       <c r="B298" t="str">
         <v>INFO</v>
       </c>
       <c r="C298" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.31s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.08s</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>2026-06-23 05:18:20</v>
+        <v>2026-06-23 05:29:42</v>
       </c>
       <c r="B299" t="str">
         <v>INFO</v>
       </c>
       <c r="C299" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.99s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.74s</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>2026-06-23 05:18:21</v>
+        <v>2026-06-23 05:29:43</v>
       </c>
       <c r="B300" t="str">
         <v>INFO</v>
       </c>
       <c r="C300" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.79s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.45s</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>2026-06-23 05:18:22</v>
+        <v>2026-06-23 05:29:44</v>
       </c>
       <c r="B301" t="str">
         <v>INFO</v>
       </c>
       <c r="C301" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.90s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.60s</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>2026-06-23 05:18:23</v>
+        <v>2026-06-23 05:29:45</v>
       </c>
       <c r="B302" t="str">
         <v>INFO</v>
       </c>
       <c r="C302" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.33s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.40s</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>2026-06-23 05:18:24</v>
+        <v>2026-06-23 05:29:46</v>
       </c>
       <c r="B303" t="str">
         <v>INFO</v>
       </c>
       <c r="C303" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.40s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.91s</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>2026-06-23 05:18:25</v>
+        <v>2026-06-23 05:29:47</v>
       </c>
       <c r="B304" t="str">
         <v>INFO</v>
       </c>
       <c r="C304" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.25s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.80s</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>2026-06-23 05:18:26</v>
+        <v>2026-06-23 05:29:48</v>
       </c>
       <c r="B305" t="str">
         <v>INFO</v>
       </c>
       <c r="C305" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.91s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.29s</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>2026-06-23 05:18:27</v>
+        <v>2026-06-23 05:29:49</v>
       </c>
       <c r="B306" t="str">
         <v>INFO</v>
       </c>
       <c r="C306" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.53s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.66s</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>2026-06-23 05:18:28</v>
+        <v>2026-06-23 05:29:50</v>
       </c>
       <c r="B307" t="str">
         <v>INFO</v>
       </c>
       <c r="C307" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.29s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.27s</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>2026-06-23 05:18:29</v>
+        <v>2026-06-23 05:29:51</v>
       </c>
       <c r="B308" t="str">
         <v>INFO</v>
       </c>
       <c r="C308" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.52s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.21s</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>2026-06-23 05:18:30</v>
+        <v>2026-06-23 05:29:52</v>
       </c>
       <c r="B309" t="str">
         <v>INFO</v>
       </c>
       <c r="C309" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.36s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.67s</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>2026-06-23 05:18:31</v>
+        <v>2026-06-23 05:29:53</v>
       </c>
       <c r="B310" t="str">
         <v>INFO</v>
       </c>
       <c r="C310" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.17s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.93s</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>2026-06-23 05:18:32</v>
+        <v>2026-06-23 05:29:54</v>
       </c>
       <c r="B311" t="str">
         <v>INFO</v>
       </c>
       <c r="C311" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.28s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.90s</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>2026-06-23 05:18:33</v>
+        <v>2026-06-23 05:29:55</v>
       </c>
       <c r="B312" t="str">
         <v>INFO</v>
       </c>
       <c r="C312" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.57s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.24s</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>2026-06-23 05:18:34</v>
+        <v>2026-06-23 05:29:56</v>
       </c>
       <c r="B313" t="str">
         <v>INFO</v>
       </c>
       <c r="C313" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.06s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.50s</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>2026-06-23 05:18:35</v>
+        <v>2026-06-23 05:29:57</v>
       </c>
       <c r="B314" t="str">
         <v>INFO</v>
       </c>
       <c r="C314" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.20s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.55s</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>2026-06-23 05:18:36</v>
+        <v>2026-06-23 05:29:58</v>
       </c>
       <c r="B315" t="str">
         <v>INFO</v>
       </c>
       <c r="C315" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.02s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.99s</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>2026-06-23 05:18:37</v>
+        <v>2026-06-23 05:29:59</v>
       </c>
       <c r="B316" t="str">
         <v>INFO</v>
       </c>
       <c r="C316" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.18s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.62s</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>2026-06-23 05:18:38</v>
+        <v>2026-06-23 05:30:00</v>
       </c>
       <c r="B317" t="str">
         <v>INFO</v>
       </c>
       <c r="C317" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.66s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.47s</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>2026-06-23 05:18:39</v>
+        <v>2026-06-23 05:30:01</v>
       </c>
       <c r="B318" t="str">
         <v>INFO</v>
       </c>
       <c r="C318" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.64s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.07s</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>2026-06-23 05:18:40</v>
+        <v>2026-06-23 05:30:02</v>
       </c>
       <c r="B319" t="str">
         <v>INFO</v>
       </c>
       <c r="C319" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.17s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.31s</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>2026-06-23 05:18:41</v>
+        <v>2026-06-23 05:30:03</v>
       </c>
       <c r="B320" t="str">
         <v>INFO</v>
       </c>
       <c r="C320" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.25s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.63s</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>2026-06-23 05:18:42</v>
+        <v>2026-06-23 05:30:04</v>
       </c>
       <c r="B321" t="str">
         <v>INFO</v>
       </c>
       <c r="C321" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.67s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.78s</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>2026-06-23 05:18:43</v>
+        <v>2026-06-23 05:30:05</v>
       </c>
       <c r="B322" t="str">
         <v>INFO</v>
       </c>
       <c r="C322" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.10s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.55s</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>2026-06-23 05:18:44</v>
+        <v>2026-06-23 05:30:06</v>
       </c>
       <c r="B323" t="str">
         <v>INFO</v>
@@ -10930,403 +10930,403 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>2026-06-23 05:18:45</v>
+        <v>2026-06-23 05:30:07</v>
       </c>
       <c r="B324" t="str">
         <v>INFO</v>
       </c>
       <c r="C324" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.46s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.64s</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>2026-06-23 05:18:46</v>
+        <v>2026-06-23 05:30:08</v>
       </c>
       <c r="B325" t="str">
         <v>INFO</v>
       </c>
       <c r="C325" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.49s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.93s</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>2026-06-23 05:18:47</v>
+        <v>2026-06-23 05:30:09</v>
       </c>
       <c r="B326" t="str">
         <v>INFO</v>
       </c>
       <c r="C326" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.61s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.08s</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>2026-06-23 05:18:48</v>
+        <v>2026-06-23 05:30:10</v>
       </c>
       <c r="B327" t="str">
         <v>INFO</v>
       </c>
       <c r="C327" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.55s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.00s</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>2026-06-23 05:18:49</v>
+        <v>2026-06-23 05:30:11</v>
       </c>
       <c r="B328" t="str">
         <v>INFO</v>
       </c>
       <c r="C328" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.75s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.76s</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>2026-06-23 05:18:50</v>
+        <v>2026-06-23 05:30:12</v>
       </c>
       <c r="B329" t="str">
         <v>INFO</v>
       </c>
       <c r="C329" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.33s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.64s</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>2026-06-23 05:18:51</v>
+        <v>2026-06-23 05:30:13</v>
       </c>
       <c r="B330" t="str">
         <v>INFO</v>
       </c>
       <c r="C330" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.03s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.52s</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>2026-06-23 05:18:52</v>
+        <v>2026-06-23 05:30:14</v>
       </c>
       <c r="B331" t="str">
         <v>INFO</v>
       </c>
       <c r="C331" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.12s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.97s</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>2026-06-23 05:18:53</v>
+        <v>2026-06-23 05:30:15</v>
       </c>
       <c r="B332" t="str">
         <v>INFO</v>
       </c>
       <c r="C332" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.40s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.65s</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>2026-06-23 05:18:54</v>
+        <v>2026-06-23 05:30:16</v>
       </c>
       <c r="B333" t="str">
         <v>INFO</v>
       </c>
       <c r="C333" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.94s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.58s</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>2026-06-23 05:18:55</v>
+        <v>2026-06-23 05:30:17</v>
       </c>
       <c r="B334" t="str">
         <v>INFO</v>
       </c>
       <c r="C334" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.23s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.88s</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>2026-06-23 05:18:56</v>
+        <v>2026-06-23 05:30:18</v>
       </c>
       <c r="B335" t="str">
         <v>INFO</v>
       </c>
       <c r="C335" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.10s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.39s</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>2026-06-23 05:18:57</v>
+        <v>2026-06-23 05:30:19</v>
       </c>
       <c r="B336" t="str">
         <v>INFO</v>
       </c>
       <c r="C336" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.31s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.46s</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>2026-06-23 05:18:58</v>
+        <v>2026-06-23 05:30:20</v>
       </c>
       <c r="B337" t="str">
         <v>INFO</v>
       </c>
       <c r="C337" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.85s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.23s</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>2026-06-23 05:18:59</v>
+        <v>2026-06-23 05:30:21</v>
       </c>
       <c r="B338" t="str">
         <v>INFO</v>
       </c>
       <c r="C338" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.52s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.39s</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>2026-06-23 05:19:00</v>
+        <v>2026-06-23 05:30:22</v>
       </c>
       <c r="B339" t="str">
         <v>INFO</v>
       </c>
       <c r="C339" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.12s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.85s</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>2026-06-23 05:19:01</v>
+        <v>2026-06-23 05:30:23</v>
       </c>
       <c r="B340" t="str">
         <v>INFO</v>
       </c>
       <c r="C340" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.34s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.14s</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>2026-06-23 05:19:02</v>
+        <v>2026-06-23 05:30:24</v>
       </c>
       <c r="B341" t="str">
         <v>INFO</v>
       </c>
       <c r="C341" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.57s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.79s</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>2026-06-23 05:19:03</v>
+        <v>2026-06-23 05:30:25</v>
       </c>
       <c r="B342" t="str">
         <v>INFO</v>
       </c>
       <c r="C342" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.57s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.92s</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>2026-06-23 05:19:04</v>
+        <v>2026-06-23 05:30:26</v>
       </c>
       <c r="B343" t="str">
         <v>INFO</v>
       </c>
       <c r="C343" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.97s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.77s</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>2026-06-23 05:19:05</v>
+        <v>2026-06-23 05:30:27</v>
       </c>
       <c r="B344" t="str">
         <v>INFO</v>
       </c>
       <c r="C344" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.03s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.68s</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>2026-06-23 05:19:06</v>
+        <v>2026-06-23 05:30:28</v>
       </c>
       <c r="B345" t="str">
         <v>INFO</v>
       </c>
       <c r="C345" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.49s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.55s</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>2026-06-23 05:19:07</v>
+        <v>2026-06-23 05:30:29</v>
       </c>
       <c r="B346" t="str">
         <v>INFO</v>
       </c>
       <c r="C346" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.68s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.07s</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>2026-06-23 05:19:08</v>
+        <v>2026-06-23 05:30:30</v>
       </c>
       <c r="B347" t="str">
         <v>INFO</v>
       </c>
       <c r="C347" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.66s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.34s</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>2026-06-23 05:19:09</v>
+        <v>2026-06-23 05:30:31</v>
       </c>
       <c r="B348" t="str">
         <v>INFO</v>
       </c>
       <c r="C348" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.06s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.09s</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>2026-06-23 05:19:10</v>
+        <v>2026-06-23 05:30:32</v>
       </c>
       <c r="B349" t="str">
         <v>INFO</v>
       </c>
       <c r="C349" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.58s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.27s</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>2026-06-23 05:19:11</v>
+        <v>2026-06-23 05:30:33</v>
       </c>
       <c r="B350" t="str">
         <v>INFO</v>
       </c>
       <c r="C350" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.85s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.46s</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>2026-06-23 05:19:12</v>
+        <v>2026-06-23 05:30:34</v>
       </c>
       <c r="B351" t="str">
         <v>INFO</v>
       </c>
       <c r="C351" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.93s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.29s</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>2026-06-23 05:19:13</v>
+        <v>2026-06-23 05:30:35</v>
       </c>
       <c r="B352" t="str">
         <v>INFO</v>
       </c>
       <c r="C352" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.83s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.06s</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>2026-06-23 05:19:14</v>
+        <v>2026-06-23 05:30:36</v>
       </c>
       <c r="B353" t="str">
         <v>INFO</v>
       </c>
       <c r="C353" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.71s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.80s</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>2026-06-23 05:19:15</v>
+        <v>2026-06-23 05:30:37</v>
       </c>
       <c r="B354" t="str">
         <v>INFO</v>
       </c>
       <c r="C354" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.18s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.64s</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>2026-06-23 05:19:16</v>
+        <v>2026-06-23 05:30:38</v>
       </c>
       <c r="B355" t="str">
         <v>INFO</v>
       </c>
       <c r="C355" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.66s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.46s</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>2026-06-23 05:19:17</v>
+        <v>2026-06-23 05:30:39</v>
       </c>
       <c r="B356" t="str">
         <v>INFO</v>
       </c>
       <c r="C356" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.62s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.02s</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>2026-06-23 05:19:18</v>
+        <v>2026-06-23 05:30:40</v>
       </c>
       <c r="B357" t="str">
         <v>INFO</v>
       </c>
       <c r="C357" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.37s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.30s</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>2026-06-23 05:19:19</v>
+        <v>2026-06-23 05:30:41</v>
       </c>
       <c r="B358" t="str">
         <v>INFO</v>
       </c>
       <c r="C358" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.20s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.18s</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>2026-06-23 05:19:20</v>
+        <v>2026-06-23 05:30:42</v>
       </c>
       <c r="B359" t="str">
         <v>INFO</v>
       </c>
       <c r="C359" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.51s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.69s</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>2026-06-23 05:19:21</v>
+        <v>2026-06-23 05:30:43</v>
       </c>
       <c r="B360" t="str">
         <v>INFO</v>
@@ -11337,453 +11337,453 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>2026-06-23 05:19:22</v>
+        <v>2026-06-23 05:30:44</v>
       </c>
       <c r="B361" t="str">
         <v>INFO</v>
       </c>
       <c r="C361" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.25s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.79s</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>2026-06-23 05:19:23</v>
+        <v>2026-06-23 05:30:45</v>
       </c>
       <c r="B362" t="str">
         <v>INFO</v>
       </c>
       <c r="C362" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.07s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.61s</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>2026-06-23 05:19:24</v>
+        <v>2026-06-23 05:30:46</v>
       </c>
       <c r="B363" t="str">
         <v>INFO</v>
       </c>
       <c r="C363" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.02s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.64s</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>2026-06-23 05:19:25</v>
+        <v>2026-06-23 05:30:47</v>
       </c>
       <c r="B364" t="str">
         <v>INFO</v>
       </c>
       <c r="C364" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.50s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.70s</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>2026-06-23 05:19:26</v>
+        <v>2026-06-23 05:30:48</v>
       </c>
       <c r="B365" t="str">
         <v>INFO</v>
       </c>
       <c r="C365" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.49s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.06s</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>2026-06-23 05:19:27</v>
+        <v>2026-06-23 05:30:49</v>
       </c>
       <c r="B366" t="str">
         <v>INFO</v>
       </c>
       <c r="C366" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.30s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.03s</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>2026-06-23 05:19:28</v>
+        <v>2026-06-23 05:30:50</v>
       </c>
       <c r="B367" t="str">
         <v>INFO</v>
       </c>
       <c r="C367" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 2.03s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.06s</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>2026-06-23 05:19:29</v>
+        <v>2026-06-23 05:30:51</v>
       </c>
       <c r="B368" t="str">
         <v>INFO</v>
       </c>
       <c r="C368" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.00s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.06s</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>2026-06-23 05:19:30</v>
+        <v>2026-06-23 05:30:52</v>
       </c>
       <c r="B369" t="str">
         <v>INFO</v>
       </c>
       <c r="C369" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.60s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.25s</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>2026-06-23 05:19:31</v>
+        <v>2026-06-23 05:30:53</v>
       </c>
       <c r="B370" t="str">
         <v>INFO</v>
       </c>
       <c r="C370" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.33s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.50s</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>2026-06-23 05:19:32</v>
+        <v>2026-06-23 05:30:54</v>
       </c>
       <c r="B371" t="str">
         <v>INFO</v>
       </c>
       <c r="C371" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.93s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.56s</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>2026-06-23 05:19:33</v>
+        <v>2026-06-23 05:30:55</v>
       </c>
       <c r="B372" t="str">
         <v>INFO</v>
       </c>
       <c r="C372" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.04s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.18s</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>2026-06-23 05:19:34</v>
+        <v>2026-06-23 05:30:56</v>
       </c>
       <c r="B373" t="str">
         <v>INFO</v>
       </c>
       <c r="C373" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.16s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.58s</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>2026-06-23 05:19:35</v>
+        <v>2026-06-23 05:30:57</v>
       </c>
       <c r="B374" t="str">
         <v>INFO</v>
       </c>
       <c r="C374" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.47s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.15s</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>2026-06-23 05:19:36</v>
+        <v>2026-06-23 05:30:58</v>
       </c>
       <c r="B375" t="str">
         <v>INFO</v>
       </c>
       <c r="C375" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.95s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.01s</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>2026-06-23 05:19:37</v>
+        <v>2026-06-23 05:30:59</v>
       </c>
       <c r="B376" t="str">
         <v>INFO</v>
       </c>
       <c r="C376" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.53s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.18s</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>2026-06-23 05:19:38</v>
+        <v>2026-06-23 05:31:00</v>
       </c>
       <c r="B377" t="str">
         <v>INFO</v>
       </c>
       <c r="C377" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.53s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.04s</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>2026-06-23 05:19:39</v>
+        <v>2026-06-23 05:31:01</v>
       </c>
       <c r="B378" t="str">
         <v>INFO</v>
       </c>
       <c r="C378" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.30s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.70s</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>2026-06-23 05:19:40</v>
+        <v>2026-06-23 05:31:02</v>
       </c>
       <c r="B379" t="str">
         <v>INFO</v>
       </c>
       <c r="C379" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.30s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.08s</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>2026-06-23 05:19:41</v>
+        <v>2026-06-23 05:31:03</v>
       </c>
       <c r="B380" t="str">
         <v>INFO</v>
       </c>
       <c r="C380" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.33s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.15s</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>2026-06-23 05:19:42</v>
+        <v>2026-06-23 05:31:04</v>
       </c>
       <c r="B381" t="str">
         <v>INFO</v>
       </c>
       <c r="C381" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.52s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.72s</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>2026-06-23 05:19:43</v>
+        <v>2026-06-23 05:31:05</v>
       </c>
       <c r="B382" t="str">
         <v>INFO</v>
       </c>
       <c r="C382" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 2.18s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.15s</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>2026-06-23 05:19:44</v>
+        <v>2026-06-23 05:31:06</v>
       </c>
       <c r="B383" t="str">
         <v>INFO</v>
       </c>
       <c r="C383" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.37s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.16s</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>2026-06-23 05:19:45</v>
+        <v>2026-06-23 05:31:07</v>
       </c>
       <c r="B384" t="str">
         <v>INFO</v>
       </c>
       <c r="C384" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.79s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.96s</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>2026-06-23 05:19:46</v>
+        <v>2026-06-23 05:31:08</v>
       </c>
       <c r="B385" t="str">
         <v>INFO</v>
       </c>
       <c r="C385" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.96s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.39s</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>2026-06-23 05:19:47</v>
+        <v>2026-06-23 05:31:09</v>
       </c>
       <c r="B386" t="str">
         <v>INFO</v>
       </c>
       <c r="C386" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.92s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 2.48s</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>2026-06-23 05:19:48</v>
+        <v>2026-06-23 05:31:10</v>
       </c>
       <c r="B387" t="str">
         <v>INFO</v>
       </c>
       <c r="C387" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 0.40s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.10s</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>2026-06-23 05:19:49</v>
+        <v>2026-06-23 05:31:11</v>
       </c>
       <c r="B388" t="str">
         <v>INFO</v>
       </c>
       <c r="C388" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.83s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 0.37s</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>2026-06-23 05:19:50</v>
+        <v>2026-06-23 05:31:12</v>
       </c>
       <c r="B389" t="str">
         <v>INFO</v>
       </c>
       <c r="C389" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 0.17s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.21s</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>2026-06-23 05:19:51</v>
+        <v>2026-06-23 05:31:13</v>
       </c>
       <c r="B390" t="str">
         <v>INFO</v>
       </c>
       <c r="C390" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.12s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 1.62s</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>2026-06-23 05:19:52</v>
+        <v>2026-06-23 05:31:14</v>
       </c>
       <c r="B391" t="str">
         <v>INFO</v>
       </c>
       <c r="C391" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.59s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 0.85s</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>2026-06-23 05:19:53</v>
+        <v>2026-06-23 05:31:15</v>
       </c>
       <c r="B392" t="str">
         <v>INFO</v>
       </c>
       <c r="C392" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.59s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 1.54s</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>2026-06-23 05:19:54</v>
+        <v>2026-06-23 05:31:16</v>
       </c>
       <c r="B393" t="str">
         <v>INFO</v>
       </c>
       <c r="C393" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 0.34s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.22s</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>2026-06-23 05:19:55</v>
+        <v>2026-06-23 05:31:17</v>
       </c>
       <c r="B394" t="str">
         <v>INFO</v>
       </c>
       <c r="C394" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.11s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 1.76s</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>2026-06-23 05:19:56</v>
+        <v>2026-06-23 05:31:18</v>
       </c>
       <c r="B395" t="str">
         <v>INFO</v>
       </c>
       <c r="C395" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.16s</v>
+        <v>[Authentication] Verify load stability on /api/auth/register → PASSED in 1.56s</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>2026-06-23 05:19:57</v>
+        <v>2026-06-23 05:31:19</v>
       </c>
       <c r="B396" t="str">
         <v>INFO</v>
       </c>
       <c r="C396" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.67s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings → PASSED in 1.35s</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>2026-06-23 05:19:58</v>
+        <v>2026-06-23 05:31:20</v>
       </c>
       <c r="B397" t="str">
         <v>INFO</v>
       </c>
       <c r="C397" t="str">
-        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 2.22s</v>
+        <v>[Core Workflow] Verify load stability on /api/bookings/my → PASSED in 0.92s</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>2026-06-23 05:19:59</v>
+        <v>2026-06-23 05:31:21</v>
       </c>
       <c r="B398" t="str">
         <v>INFO</v>
       </c>
       <c r="C398" t="str">
-        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 2.00s</v>
+        <v>[Matching System] Verify load stability on /api/bookings/match → PASSED in 1.71s</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>2026-06-23 05:20:00</v>
+        <v>2026-06-23 05:31:22</v>
       </c>
       <c r="B399" t="str">
         <v>INFO</v>
       </c>
       <c r="C399" t="str">
-        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 0.99s</v>
+        <v>[Admin Analytics] Verify load stability on /api/admin/users → PASSED in 2.07s</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>2026-06-23 05:20:01</v>
+        <v>2026-06-23 05:31:23</v>
       </c>
       <c r="B400" t="str">
         <v>INFO</v>
       </c>
       <c r="C400" t="str">
-        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.69s</v>
+        <v>[Health Check] Verify load stability on /api/health → PASSED in 1.49s</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>2026-06-23 05:20:02</v>
+        <v>2026-06-23 05:31:24</v>
       </c>
       <c r="B401" t="str">
         <v>INFO</v>
       </c>
       <c r="C401" t="str">
-        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.19s</v>
+        <v>[Authentication] Verify load stability on /api/auth/login → PASSED in 2.14s</v>
       </c>
     </row>
   </sheetData>
